--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11960"/>
+    <workbookView windowWidth="17145" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
     <t>mcjthoto</t>
   </si>
   <si>
-    <t>23.229.91.44:6477:lfxwowly:2ve2stnj09xk</t>
+    <t>72.1.178.77:6971:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
     <t>nantktlady@gmail.com</t>
@@ -1658,12 +1658,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="36.0576923076923" customWidth="1"/>
-    <col min="2" max="2" width="20.3557692307692" customWidth="1"/>
-    <col min="3" max="3" width="21.3173076923077" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43.5865384615385" customWidth="1"/>
+    <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
+    <col min="2" max="2" width="20.3583333333333" customWidth="1"/>
+    <col min="3" max="3" width="21.3166666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="39" customHeight="1" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" ht="15" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="15" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" ht="15" spans="1:4">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" ht="15" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" ht="15" spans="1:4">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" ht="15" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" ht="15" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" ht="15" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" ht="15" spans="1:4">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" ht="15" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" ht="15" spans="1:4">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" ht="15" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" ht="15" spans="1:4">
       <c r="A14" s="6" t="s">
         <v>33</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" ht="15" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>36</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" ht="15" spans="1:4">
       <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" ht="15" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" ht="15" spans="1:4">
       <c r="A18" s="3" t="s">
         <v>43</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" ht="15" spans="1:4">
       <c r="A19" s="3" t="s">
         <v>45</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" ht="15" spans="1:4">
       <c r="A20" s="3" t="s">
         <v>47</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" ht="15" spans="1:4">
       <c r="A21" s="3" t="s">
         <v>50</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" ht="15" spans="1:4">
       <c r="A22" s="3" t="s">
         <v>52</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" ht="15" spans="1:4">
       <c r="A23" s="3" t="s">
         <v>54</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" ht="15" spans="1:4">
       <c r="A24" s="3" t="s">
         <v>57</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" ht="15" spans="1:4">
       <c r="A25" s="3" t="s">
         <v>59</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" ht="15" spans="1:4">
       <c r="A26" s="3" t="s">
         <v>61</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" ht="15" spans="1:4">
       <c r="A27" s="3" t="s">
         <v>64</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" ht="15" spans="1:4">
       <c r="A28" s="3" t="s">
         <v>66</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" ht="15" spans="1:4">
       <c r="A29" s="3" t="s">
         <v>68</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" ht="15" spans="1:4">
       <c r="A30" s="3" t="s">
         <v>71</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" ht="15" spans="1:4">
       <c r="A31" s="3" t="s">
         <v>73</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" ht="15" spans="1:4">
       <c r="A32" s="3" t="s">
         <v>75</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" ht="15" spans="1:4">
       <c r="A33" s="3" t="s">
         <v>78</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" ht="15" spans="1:4">
       <c r="A34" s="3" t="s">
         <v>80</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" ht="15" spans="1:4">
       <c r="A35" s="3" t="s">
         <v>82</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" ht="15" spans="1:4">
       <c r="A36" s="3" t="s">
         <v>85</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" ht="15" spans="1:4">
       <c r="A37" s="3" t="s">
         <v>87</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" ht="15" spans="1:4">
       <c r="A38" s="3" t="s">
         <v>89</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" ht="15" spans="1:4">
       <c r="A39" s="3" t="s">
         <v>92</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" ht="15" spans="1:4">
       <c r="A40" s="3" t="s">
         <v>94</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" ht="15" spans="1:4">
       <c r="A41" s="3" t="s">
         <v>96</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" ht="15" spans="1:4">
       <c r="A42" s="3" t="s">
         <v>99</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" ht="15" spans="1:4">
       <c r="A43" s="3" t="s">
         <v>101</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" ht="15" spans="1:4">
       <c r="A44" s="3" t="s">
         <v>103</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" ht="15" spans="1:4">
       <c r="A45" s="3" t="s">
         <v>106</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" ht="15" spans="1:4">
       <c r="A46" s="3" t="s">
         <v>108</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" ht="15" spans="1:4">
       <c r="A47" s="3" t="s">
         <v>110</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" ht="15" spans="1:4">
       <c r="A48" s="3" t="s">
         <v>113</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" ht="15" spans="1:4">
       <c r="A49" s="3" t="s">
         <v>115</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" ht="15" spans="1:4">
       <c r="A50" s="3" t="s">
         <v>117</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" ht="15" spans="1:4">
       <c r="A51" s="3" t="s">
         <v>120</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" ht="15" spans="1:4">
       <c r="A52" s="3" t="s">
         <v>122</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" ht="15" spans="1:4">
       <c r="A53" s="3" t="s">
         <v>124</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" ht="15" spans="1:4">
       <c r="A54" s="3" t="s">
         <v>127</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" ht="15" spans="1:4">
       <c r="A55" s="3" t="s">
         <v>129</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" ht="15" spans="1:4">
       <c r="A56" s="3" t="s">
         <v>131</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" ht="15" spans="1:4">
       <c r="A57" s="3" t="s">
         <v>134</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" ht="15" spans="1:4">
       <c r="A58" s="3" t="s">
         <v>136</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" ht="15" spans="1:4">
       <c r="A59" s="3" t="s">
         <v>138</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" ht="15" spans="1:4">
       <c r="A60" s="3" t="s">
         <v>141</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" ht="15" spans="1:4">
       <c r="A61" s="3" t="s">
         <v>143</v>
       </c>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17145" windowHeight="9675"/>
+    <workbookView windowWidth="17385" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="144">
   <si>
     <t>email</t>
   </si>
@@ -426,9 +426,6 @@
   </si>
   <si>
     <t>wmyasin</t>
-  </si>
-  <si>
-    <t>23.229.91.184:6617:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
     <t>emrahkaravus2011@hotmail.com</t>
@@ -2447,77 +2444,77 @@
         <v>6</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" ht="15" spans="1:4">
       <c r="A57" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="C57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" ht="15" spans="1:4">
       <c r="A58" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="C58" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" ht="15" spans="1:4">
       <c r="A59" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="60" ht="15" spans="1:4">
       <c r="A60" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="C60" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" ht="15" spans="1:4">
       <c r="A61" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C61" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17385" windowHeight="10260"/>
+    <workbookView windowWidth="17625" windowHeight="10845"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="145">
   <si>
     <t>email</t>
   </si>
@@ -71,361 +71,364 @@
     <t>mcjthoto</t>
   </si>
   <si>
+    <t>45.56.176.3:7581:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>nantktlady@gmail.com</t>
+  </si>
+  <si>
+    <t>nantktlady</t>
+  </si>
+  <si>
+    <t>babaa_akdemir12@hotmail.com</t>
+  </si>
+  <si>
+    <t>babaaakdemir12</t>
+  </si>
+  <si>
+    <t>babulijo7@gmail.com</t>
+  </si>
+  <si>
+    <t>lijobabucr</t>
+  </si>
+  <si>
+    <t>72.1.178.176:7070:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>akrepali_06@windowslive.com</t>
+  </si>
+  <si>
+    <t>alikr11</t>
+  </si>
+  <si>
+    <t>rachaelbeyor@gmail.com</t>
+  </si>
+  <si>
+    <t>rbeyor28</t>
+  </si>
+  <si>
+    <t>tanvimaan@yahoo.in</t>
+  </si>
+  <si>
+    <t>tanvimaan</t>
+  </si>
+  <si>
+    <t>45.56.176.73:7651:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>lewagner1965@gmail.com</t>
+  </si>
+  <si>
+    <t>lewagner1965</t>
+  </si>
+  <si>
+    <t>paullechien@gmail.com</t>
+  </si>
+  <si>
+    <t>paullechien</t>
+  </si>
+  <si>
+    <t>riazhussain_36@gmil.com</t>
+  </si>
+  <si>
+    <t>riazhussain36</t>
+  </si>
+  <si>
+    <t>72.1.178.209:7103:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>daniela_chulis@hotmail.com</t>
+  </si>
+  <si>
+    <t>chulis_maria</t>
+  </si>
+  <si>
+    <t>matty_2147@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>matty2147</t>
+  </si>
+  <si>
+    <t>arranyounger90@yahoo.co.uk</t>
+  </si>
+  <si>
+    <t>arranyounger</t>
+  </si>
+  <si>
+    <t>72.1.178.26:6920:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>laasecina_17@hotmail.com</t>
+  </si>
+  <si>
+    <t>nallely05j</t>
+  </si>
+  <si>
+    <t>recepkalkavan@gmail.com</t>
+  </si>
+  <si>
+    <t>recepkalkavan</t>
+  </si>
+  <si>
+    <t>korbinian.kraus@live.de</t>
+  </si>
+  <si>
+    <t>korbiniankraus</t>
+  </si>
+  <si>
+    <t>45.56.176.224:7802:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>elina.glittmark@hotmail.com</t>
+  </si>
+  <si>
+    <t>elinaglittmark</t>
+  </si>
+  <si>
+    <t>murilolenotti@gmail.com</t>
+  </si>
+  <si>
+    <t>murilolenotti</t>
+  </si>
+  <si>
+    <t>pepe.moto@live.cl</t>
+  </si>
+  <si>
+    <t>pepemoto</t>
+  </si>
+  <si>
+    <t>45.56.176.227:7805:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>xokrystinavxo@aim.com</t>
+  </si>
+  <si>
+    <t>kvizard</t>
+  </si>
+  <si>
+    <t>dibernado@naver.com</t>
+  </si>
+  <si>
+    <t>dibernado</t>
+  </si>
+  <si>
+    <t>ibrahimyakuburaji@yahoo.com</t>
+  </si>
+  <si>
+    <t>ibwizkid</t>
+  </si>
+  <si>
+    <t>72.1.178.115:7009:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>juniorsimons123@gmail.com</t>
+  </si>
+  <si>
+    <t>juniorsimons123</t>
+  </si>
+  <si>
+    <t>iorirahim@ymail.com</t>
+  </si>
+  <si>
+    <t>iorirahim</t>
+  </si>
+  <si>
+    <t>aungsitun53@mail.com</t>
+  </si>
+  <si>
+    <t>aungsitun</t>
+  </si>
+  <si>
+    <t>45.56.176.240:7818:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>niklajj60@mail.ru</t>
+  </si>
+  <si>
+    <t>niklajj60</t>
+  </si>
+  <si>
+    <t>prince_oc2000@hotmail.com</t>
+  </si>
+  <si>
+    <t>princechigbu</t>
+  </si>
+  <si>
+    <t>dalkiel_dark666@hitmail.com</t>
+  </si>
+  <si>
+    <t>dalkieldark666</t>
+  </si>
+  <si>
+    <t>72.1.178.183:7077:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>hurbbieirving13@yahoo.co</t>
+  </si>
+  <si>
+    <t>hurbbieirving</t>
+  </si>
+  <si>
+    <t>bilbaina14@gmail.com</t>
+  </si>
+  <si>
+    <t>bilbaina14</t>
+  </si>
+  <si>
+    <t>uak_nhk@rediffmail.com</t>
+  </si>
+  <si>
+    <t>uaknhkvamshi</t>
+  </si>
+  <si>
+    <t>45.56.176.27:7605:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>alberodamian90@gmail.com</t>
+  </si>
+  <si>
+    <t>albertodamian90</t>
+  </si>
+  <si>
+    <t>mohamedkazaz88@yahoo.com</t>
+  </si>
+  <si>
+    <t>mohamed46260908</t>
+  </si>
+  <si>
+    <t>rosehardly@yhoo.com</t>
+  </si>
+  <si>
+    <t>rosehardly</t>
+  </si>
+  <si>
+    <t>72.1.178.194:7088:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>loveseey@live.co.uk</t>
+  </si>
+  <si>
+    <t>jakelovesey</t>
+  </si>
+  <si>
+    <t>jukutkesong@ovi.com</t>
+  </si>
+  <si>
+    <t>mitaaditia</t>
+  </si>
+  <si>
+    <t>patleddy5@gmail.com</t>
+  </si>
+  <si>
+    <t>patleddy5</t>
+  </si>
+  <si>
+    <t>72.1.178.231:7125:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>erinbraaton9@gmail.com</t>
+  </si>
+  <si>
+    <t>erinbratton</t>
+  </si>
+  <si>
+    <t>annimeba@gmail.com</t>
+  </si>
+  <si>
+    <t>annimeba</t>
+  </si>
+  <si>
+    <t>calenciamay@yahoo.com</t>
+  </si>
+  <si>
+    <t>calenciamay</t>
+  </si>
+  <si>
+    <t>45.56.176.250:7828:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>ophelie.lamotte@hayoo.fr</t>
+  </si>
+  <si>
+    <t>ophelielamotte</t>
+  </si>
+  <si>
+    <t>anabursac98@gmail.com</t>
+  </si>
+  <si>
+    <t>abursac98</t>
+  </si>
+  <si>
+    <t>www.eliabath@2002.com</t>
+  </si>
+  <si>
+    <t>corbinmckee</t>
+  </si>
+  <si>
+    <t>72.1.178.162:7056:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>zuzum_3mo@hotmail.com</t>
+  </si>
+  <si>
+    <t>kaderozcan</t>
+  </si>
+  <si>
+    <t>mikemarold1974@cox.net</t>
+  </si>
+  <si>
+    <t>mikemarold</t>
+  </si>
+  <si>
+    <t>matikamil1998@gmail.com</t>
+  </si>
+  <si>
+    <t>rayvi988</t>
+  </si>
+  <si>
+    <t>45.56.176.210:7788:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>lina.osfour94@gmail.com</t>
+  </si>
+  <si>
+    <t>linaosfour</t>
+  </si>
+  <si>
+    <t>auradesousa@gmail.com</t>
+  </si>
+  <si>
+    <t>auradesousa</t>
+  </si>
+  <si>
+    <t>hlahatra@gmail.com</t>
+  </si>
+  <si>
+    <t>lahatraharizo</t>
+  </si>
+  <si>
+    <t>45.56.176.53:7631:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>gus.popotito@gmail.com</t>
+  </si>
+  <si>
+    <t>guspopotito</t>
+  </si>
+  <si>
+    <t>kiona.mcneil@yaoo.com</t>
+  </si>
+  <si>
+    <t>kionamcneil</t>
+  </si>
+  <si>
+    <t>abu_syafaat@twitter.com</t>
+  </si>
+  <si>
+    <t>wmyasin</t>
+  </si>
+  <si>
     <t>72.1.178.77:6971:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>nantktlady@gmail.com</t>
-  </si>
-  <si>
-    <t>nantktlady</t>
-  </si>
-  <si>
-    <t>babaa_akdemir12@hotmail.com</t>
-  </si>
-  <si>
-    <t>babaaakdemir12</t>
-  </si>
-  <si>
-    <t>babulijo7@gmail.com</t>
-  </si>
-  <si>
-    <t>lijobabucr</t>
-  </si>
-  <si>
-    <t>72.1.178.176:7070:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>akrepali_06@windowslive.com</t>
-  </si>
-  <si>
-    <t>alikr11</t>
-  </si>
-  <si>
-    <t>rachaelbeyor@gmail.com</t>
-  </si>
-  <si>
-    <t>rbeyor28</t>
-  </si>
-  <si>
-    <t>tanvimaan@yahoo.in</t>
-  </si>
-  <si>
-    <t>tanvimaan</t>
-  </si>
-  <si>
-    <t>45.56.176.73:7651:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>lewagner1965@gmail.com</t>
-  </si>
-  <si>
-    <t>lewagner1965</t>
-  </si>
-  <si>
-    <t>paullechien@gmail.com</t>
-  </si>
-  <si>
-    <t>paullechien</t>
-  </si>
-  <si>
-    <t>riazhussain_36@gmil.com</t>
-  </si>
-  <si>
-    <t>riazhussain36</t>
-  </si>
-  <si>
-    <t>72.1.178.209:7103:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>daniela_chulis@hotmail.com</t>
-  </si>
-  <si>
-    <t>chulis_maria</t>
-  </si>
-  <si>
-    <t>matty_2147@hotmail.com.ar</t>
-  </si>
-  <si>
-    <t>matty2147</t>
-  </si>
-  <si>
-    <t>arranyounger90@yahoo.co.uk</t>
-  </si>
-  <si>
-    <t>arranyounger</t>
-  </si>
-  <si>
-    <t>72.1.178.26:6920:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>laasecina_17@hotmail.com</t>
-  </si>
-  <si>
-    <t>nallely05j</t>
-  </si>
-  <si>
-    <t>recepkalkavan@gmail.com</t>
-  </si>
-  <si>
-    <t>recepkalkavan</t>
-  </si>
-  <si>
-    <t>korbinian.kraus@live.de</t>
-  </si>
-  <si>
-    <t>korbiniankraus</t>
-  </si>
-  <si>
-    <t>45.56.176.224:7802:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>elina.glittmark@hotmail.com</t>
-  </si>
-  <si>
-    <t>elinaglittmark</t>
-  </si>
-  <si>
-    <t>murilolenotti@gmail.com</t>
-  </si>
-  <si>
-    <t>murilolenotti</t>
-  </si>
-  <si>
-    <t>pepe.moto@live.cl</t>
-  </si>
-  <si>
-    <t>pepemoto</t>
-  </si>
-  <si>
-    <t>45.56.176.227:7805:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>xokrystinavxo@aim.com</t>
-  </si>
-  <si>
-    <t>kvizard</t>
-  </si>
-  <si>
-    <t>dibernado@naver.com</t>
-  </si>
-  <si>
-    <t>dibernado</t>
-  </si>
-  <si>
-    <t>ibrahimyakuburaji@yahoo.com</t>
-  </si>
-  <si>
-    <t>ibwizkid</t>
-  </si>
-  <si>
-    <t>72.1.178.115:7009:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>juniorsimons123@gmail.com</t>
-  </si>
-  <si>
-    <t>juniorsimons123</t>
-  </si>
-  <si>
-    <t>iorirahim@ymail.com</t>
-  </si>
-  <si>
-    <t>iorirahim</t>
-  </si>
-  <si>
-    <t>aungsitun53@mail.com</t>
-  </si>
-  <si>
-    <t>aungsitun</t>
-  </si>
-  <si>
-    <t>45.56.176.240:7818:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>niklajj60@mail.ru</t>
-  </si>
-  <si>
-    <t>niklajj60</t>
-  </si>
-  <si>
-    <t>prince_oc2000@hotmail.com</t>
-  </si>
-  <si>
-    <t>princechigbu</t>
-  </si>
-  <si>
-    <t>dalkiel_dark666@hitmail.com</t>
-  </si>
-  <si>
-    <t>dalkieldark666</t>
-  </si>
-  <si>
-    <t>72.1.178.183:7077:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>hurbbieirving13@yahoo.co</t>
-  </si>
-  <si>
-    <t>hurbbieirving</t>
-  </si>
-  <si>
-    <t>bilbaina14@gmail.com</t>
-  </si>
-  <si>
-    <t>bilbaina14</t>
-  </si>
-  <si>
-    <t>uak_nhk@rediffmail.com</t>
-  </si>
-  <si>
-    <t>uaknhkvamshi</t>
-  </si>
-  <si>
-    <t>45.56.176.27:7605:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>alberodamian90@gmail.com</t>
-  </si>
-  <si>
-    <t>albertodamian90</t>
-  </si>
-  <si>
-    <t>mohamedkazaz88@yahoo.com</t>
-  </si>
-  <si>
-    <t>mohamed46260908</t>
-  </si>
-  <si>
-    <t>rosehardly@yhoo.com</t>
-  </si>
-  <si>
-    <t>rosehardly</t>
-  </si>
-  <si>
-    <t>72.1.178.194:7088:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>loveseey@live.co.uk</t>
-  </si>
-  <si>
-    <t>jakelovesey</t>
-  </si>
-  <si>
-    <t>jukutkesong@ovi.com</t>
-  </si>
-  <si>
-    <t>mitaaditia</t>
-  </si>
-  <si>
-    <t>patleddy5@gmail.com</t>
-  </si>
-  <si>
-    <t>patleddy5</t>
-  </si>
-  <si>
-    <t>72.1.178.231:7125:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>erinbraaton9@gmail.com</t>
-  </si>
-  <si>
-    <t>erinbratton</t>
-  </si>
-  <si>
-    <t>annimeba@gmail.com</t>
-  </si>
-  <si>
-    <t>annimeba</t>
-  </si>
-  <si>
-    <t>calenciamay@yahoo.com</t>
-  </si>
-  <si>
-    <t>calenciamay</t>
-  </si>
-  <si>
-    <t>45.56.176.250:7828:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>ophelie.lamotte@hayoo.fr</t>
-  </si>
-  <si>
-    <t>ophelielamotte</t>
-  </si>
-  <si>
-    <t>anabursac98@gmail.com</t>
-  </si>
-  <si>
-    <t>abursac98</t>
-  </si>
-  <si>
-    <t>www.eliabath@2002.com</t>
-  </si>
-  <si>
-    <t>corbinmckee</t>
-  </si>
-  <si>
-    <t>72.1.178.162:7056:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>zuzum_3mo@hotmail.com</t>
-  </si>
-  <si>
-    <t>kaderozcan</t>
-  </si>
-  <si>
-    <t>mikemarold1974@cox.net</t>
-  </si>
-  <si>
-    <t>mikemarold</t>
-  </si>
-  <si>
-    <t>matikamil1998@gmail.com</t>
-  </si>
-  <si>
-    <t>rayvi988</t>
-  </si>
-  <si>
-    <t>45.56.176.210:7788:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>lina.osfour94@gmail.com</t>
-  </si>
-  <si>
-    <t>linaosfour</t>
-  </si>
-  <si>
-    <t>auradesousa@gmail.com</t>
-  </si>
-  <si>
-    <t>auradesousa</t>
-  </si>
-  <si>
-    <t>hlahatra@gmail.com</t>
-  </si>
-  <si>
-    <t>lahatraharizo</t>
-  </si>
-  <si>
-    <t>45.56.176.53:7631:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>gus.popotito@gmail.com</t>
-  </si>
-  <si>
-    <t>guspopotito</t>
-  </si>
-  <si>
-    <t>kiona.mcneil@yaoo.com</t>
-  </si>
-  <si>
-    <t>kionamcneil</t>
-  </si>
-  <si>
-    <t>abu_syafaat@twitter.com</t>
-  </si>
-  <si>
-    <t>wmyasin</t>
   </si>
   <si>
     <t>emrahkaravus2011@hotmail.com</t>
@@ -2444,77 +2447,77 @@
         <v>6</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" ht="15" spans="1:4">
       <c r="A57" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="58" ht="15" spans="1:4">
       <c r="A58" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" ht="15" spans="1:4">
       <c r="A59" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" ht="15" spans="1:4">
       <c r="A60" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="61" ht="15" spans="1:4">
       <c r="A61" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17625" windowHeight="10845"/>
+    <workbookView windowWidth="26475" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="138">
   <si>
     <t>email</t>
   </si>
@@ -41,427 +41,406 @@
     <t>residential_proxy</t>
   </si>
   <si>
-    <t>ella.gevondyan@twitter.ru</t>
-  </si>
-  <si>
-    <t>ellagevondyan</t>
-  </si>
-  <si>
-    <t>Asd001122@djt</t>
+    <t>moorental@gmail.com</t>
+  </si>
+  <si>
+    <t>moorental</t>
+  </si>
+  <si>
+    <t>Y5bIKueZX7CVtlp</t>
   </si>
   <si>
     <t>45.56.176.128:7706:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>dafeny@mail.com</t>
-  </si>
-  <si>
-    <t>desireemahone</t>
-  </si>
-  <si>
-    <t>francenag@yahoo.com</t>
-  </si>
-  <si>
-    <t>francenag</t>
-  </si>
-  <si>
-    <t>mcjthoto@yahoo.com</t>
-  </si>
-  <si>
-    <t>mcjthoto</t>
+    <t>miguelmac1986@hotnail.com</t>
+  </si>
+  <si>
+    <t>miguelmac1986</t>
+  </si>
+  <si>
+    <t>xNEDSaonyvkiQV</t>
+  </si>
+  <si>
+    <t>sunnny.deep123@gmail.com</t>
+  </si>
+  <si>
+    <t>sunnydeep123</t>
+  </si>
+  <si>
+    <t>4gm7qaxRGBudbWM</t>
+  </si>
+  <si>
+    <t>lwaine84@gmail.com</t>
+  </si>
+  <si>
+    <t>lwaine84</t>
+  </si>
+  <si>
+    <t>r6yhjbdwZNFuMPR1V</t>
   </si>
   <si>
     <t>45.56.176.3:7581:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>nantktlady@gmail.com</t>
-  </si>
-  <si>
-    <t>nantktlady</t>
-  </si>
-  <si>
-    <t>babaa_akdemir12@hotmail.com</t>
-  </si>
-  <si>
-    <t>babaaakdemir12</t>
-  </si>
-  <si>
-    <t>babulijo7@gmail.com</t>
-  </si>
-  <si>
-    <t>lijobabucr</t>
+    <t>randy-2009@live.fr</t>
+  </si>
+  <si>
+    <t>randysoumahoro</t>
+  </si>
+  <si>
+    <t>hzL4wNtsicorOleYm</t>
+  </si>
+  <si>
+    <t>stefanweeds@mail.ru</t>
+  </si>
+  <si>
+    <t>stefanweeds</t>
+  </si>
+  <si>
+    <t>UlRnCfAusXZqjpi</t>
+  </si>
+  <si>
+    <t>nasipbaba55@hotmail.com</t>
+  </si>
+  <si>
+    <t>nasiptorun</t>
+  </si>
+  <si>
+    <t>WM5s34HGuSzh9D</t>
   </si>
   <si>
     <t>72.1.178.176:7070:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>akrepali_06@windowslive.com</t>
-  </si>
-  <si>
-    <t>alikr11</t>
-  </si>
-  <si>
-    <t>rachaelbeyor@gmail.com</t>
-  </si>
-  <si>
-    <t>rbeyor28</t>
-  </si>
-  <si>
-    <t>tanvimaan@yahoo.in</t>
-  </si>
-  <si>
-    <t>tanvimaan</t>
+    <t>taytu1704@gmail.com</t>
+  </si>
+  <si>
+    <t>taytu1704</t>
+  </si>
+  <si>
+    <t>3bPvDw87LJCliR</t>
+  </si>
+  <si>
+    <t>jessicagema@gmail.com</t>
+  </si>
+  <si>
+    <t>jessicagema</t>
+  </si>
+  <si>
+    <t>WB89johV51YNrzyPv</t>
+  </si>
+  <si>
+    <t>littlehand19@gmail.com</t>
+  </si>
+  <si>
+    <t>littlehand19</t>
+  </si>
+  <si>
+    <t>0HNejaOUqXrCRD</t>
   </si>
   <si>
     <t>45.56.176.73:7651:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>lewagner1965@gmail.com</t>
-  </si>
-  <si>
-    <t>lewagner1965</t>
-  </si>
-  <si>
-    <t>paullechien@gmail.com</t>
-  </si>
-  <si>
-    <t>paullechien</t>
-  </si>
-  <si>
-    <t>riazhussain_36@gmil.com</t>
-  </si>
-  <si>
-    <t>riazhussain36</t>
+    <t>codey09@hotmail.com</t>
+  </si>
+  <si>
+    <t>dlodge70</t>
+  </si>
+  <si>
+    <t>2JI5YWfXqOa4CFn</t>
+  </si>
+  <si>
+    <t>jotelantwi@gmail.com</t>
+  </si>
+  <si>
+    <t>jotelantwi</t>
+  </si>
+  <si>
+    <t>HXu9eOBz71dk2ZR6</t>
+  </si>
+  <si>
+    <t>su.sergeev@yandex.ru</t>
+  </si>
+  <si>
+    <t>susergeev</t>
+  </si>
+  <si>
+    <t>ktBrRwuyvb2ljeITZ8</t>
   </si>
   <si>
     <t>72.1.178.209:7103:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>daniela_chulis@hotmail.com</t>
-  </si>
-  <si>
-    <t>chulis_maria</t>
-  </si>
-  <si>
-    <t>matty_2147@hotmail.com.ar</t>
-  </si>
-  <si>
-    <t>matty2147</t>
-  </si>
-  <si>
-    <t>arranyounger90@yahoo.co.uk</t>
-  </si>
-  <si>
-    <t>arranyounger</t>
+    <t>sonu.rajput60@yahoo.in</t>
+  </si>
+  <si>
+    <t>sonujamuniya</t>
+  </si>
+  <si>
+    <t>ZgM9uxls7WPRpBCJ</t>
+  </si>
+  <si>
+    <t>ruly_ippo@yaoo.com</t>
+  </si>
+  <si>
+    <t>rulyippo</t>
+  </si>
+  <si>
+    <t>w6RZSoMTGdkqpK</t>
+  </si>
+  <si>
+    <t>bondflr222@gmail.com</t>
+  </si>
+  <si>
+    <t>bondflr22</t>
+  </si>
+  <si>
+    <t>jTfWyGJMvhbISduD5</t>
   </si>
   <si>
     <t>72.1.178.26:6920:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>laasecina_17@hotmail.com</t>
-  </si>
-  <si>
-    <t>nallely05j</t>
-  </si>
-  <si>
-    <t>recepkalkavan@gmail.com</t>
-  </si>
-  <si>
-    <t>recepkalkavan</t>
-  </si>
-  <si>
-    <t>korbinian.kraus@live.de</t>
-  </si>
-  <si>
-    <t>korbiniankraus</t>
+    <t>cianabanana@icloud.com</t>
+  </si>
+  <si>
+    <t>cianamadigan</t>
+  </si>
+  <si>
+    <t>WeEtq7VXpPudAKF</t>
+  </si>
+  <si>
+    <t>gissels_linares@hotmail.com</t>
+  </si>
+  <si>
+    <t>gisselalinares</t>
+  </si>
+  <si>
+    <t>neQFzyIVp2bTRYESC</t>
+  </si>
+  <si>
+    <t>doop1111@hotmail.co.uk</t>
+  </si>
+  <si>
+    <t>kierancuthbert</t>
+  </si>
+  <si>
+    <t>BGoORDnmeQWJTEp</t>
   </si>
   <si>
     <t>45.56.176.224:7802:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>elina.glittmark@hotmail.com</t>
-  </si>
-  <si>
-    <t>elinaglittmark</t>
-  </si>
-  <si>
-    <t>murilolenotti@gmail.com</t>
-  </si>
-  <si>
-    <t>murilolenotti</t>
-  </si>
-  <si>
-    <t>pepe.moto@live.cl</t>
-  </si>
-  <si>
-    <t>pepemoto</t>
+    <t>cdavid2489@gmail.com</t>
+  </si>
+  <si>
+    <t>cdavid2489</t>
+  </si>
+  <si>
+    <t>IHO6PCGMVviu0hNJ7K</t>
+  </si>
+  <si>
+    <t>yassirbajaber@gmail.com</t>
+  </si>
+  <si>
+    <t>yassirbajaber</t>
+  </si>
+  <si>
+    <t>ie5SyFs8n0Rr9VEwOX</t>
+  </si>
+  <si>
+    <t>tania.sharma57@gmail.com</t>
+  </si>
+  <si>
+    <t>maneetsangwan</t>
+  </si>
+  <si>
+    <t>6QZ3emxE5AN8K1HU9q</t>
   </si>
   <si>
     <t>45.56.176.227:7805:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>xokrystinavxo@aim.com</t>
-  </si>
-  <si>
-    <t>kvizard</t>
-  </si>
-  <si>
-    <t>dibernado@naver.com</t>
-  </si>
-  <si>
-    <t>dibernado</t>
-  </si>
-  <si>
-    <t>ibrahimyakuburaji@yahoo.com</t>
-  </si>
-  <si>
-    <t>ibwizkid</t>
+    <t>memo.hope.sy@hotmail.com</t>
+  </si>
+  <si>
+    <t>magedgashem</t>
+  </si>
+  <si>
+    <t>w3yxFkYHWNnjepzc</t>
+  </si>
+  <si>
+    <t>edwardsterrazzo@gmail.com</t>
+  </si>
+  <si>
+    <t>edwardsterrazzo</t>
+  </si>
+  <si>
+    <t>Hhvtlzu2Tr3VK6fG1i</t>
+  </si>
+  <si>
+    <t>solovictor1997@gmail.com</t>
+  </si>
+  <si>
+    <t>solovictor1997</t>
+  </si>
+  <si>
+    <t>bN2wLxPjGVWB1diu</t>
   </si>
   <si>
     <t>72.1.178.115:7009:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>juniorsimons123@gmail.com</t>
-  </si>
-  <si>
-    <t>juniorsimons123</t>
-  </si>
-  <si>
-    <t>iorirahim@ymail.com</t>
-  </si>
-  <si>
-    <t>iorirahim</t>
-  </si>
-  <si>
-    <t>aungsitun53@mail.com</t>
-  </si>
-  <si>
-    <t>aungsitun</t>
+    <t>willams_gatinho13@hotmail.com</t>
+  </si>
+  <si>
+    <t>maxrdb</t>
+  </si>
+  <si>
+    <t>IBskz7YJjndaf6v4H5</t>
+  </si>
+  <si>
+    <t>omar-naqi@hotmail.com</t>
+  </si>
+  <si>
+    <t>omarnaqi</t>
+  </si>
+  <si>
+    <t>A0oiH5gPDaW4uVT2</t>
+  </si>
+  <si>
+    <t>satta_ginanjar@yahoo.com</t>
+  </si>
+  <si>
+    <t>sattagitarist</t>
+  </si>
+  <si>
+    <t>uhxICKAzwpO5DV0</t>
   </si>
   <si>
     <t>45.56.176.240:7818:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>niklajj60@mail.ru</t>
-  </si>
-  <si>
-    <t>niklajj60</t>
-  </si>
-  <si>
-    <t>prince_oc2000@hotmail.com</t>
-  </si>
-  <si>
-    <t>princechigbu</t>
-  </si>
-  <si>
-    <t>dalkiel_dark666@hitmail.com</t>
-  </si>
-  <si>
-    <t>dalkieldark666</t>
+    <t>ofwallace@gmail.com</t>
+  </si>
+  <si>
+    <t>ofwallace</t>
+  </si>
+  <si>
+    <t>KvYLgt0r91n46PhSVX</t>
+  </si>
+  <si>
+    <t>beesley378@btinternet.com</t>
+  </si>
+  <si>
+    <t>beesley378</t>
+  </si>
+  <si>
+    <t>Fhgv7kYENZbUT2d</t>
+  </si>
+  <si>
+    <t>mathiasblitz@gmail.com</t>
+  </si>
+  <si>
+    <t>mathiasblitz</t>
+  </si>
+  <si>
+    <t>ZY5rs7IXAHRUtxQae</t>
   </si>
   <si>
     <t>72.1.178.183:7077:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>hurbbieirving13@yahoo.co</t>
-  </si>
-  <si>
-    <t>hurbbieirving</t>
-  </si>
-  <si>
-    <t>bilbaina14@gmail.com</t>
-  </si>
-  <si>
-    <t>bilbaina14</t>
-  </si>
-  <si>
-    <t>uak_nhk@rediffmail.com</t>
-  </si>
-  <si>
-    <t>uaknhkvamshi</t>
+    <t>mlgerloff@gmail.com</t>
+  </si>
+  <si>
+    <t>michelegerloff</t>
+  </si>
+  <si>
+    <t>cuH1qldBn8OUXhMf2i</t>
+  </si>
+  <si>
+    <t>eidenpauli@gmail.fr</t>
+  </si>
+  <si>
+    <t>paulieiden</t>
+  </si>
+  <si>
+    <t>ylpD8XZ0QrWhCae6</t>
+  </si>
+  <si>
+    <t>saidben1306@gmail.com</t>
+  </si>
+  <si>
+    <t>saidben1306</t>
+  </si>
+  <si>
+    <t>Xrn7jvilSquhTO</t>
   </si>
   <si>
     <t>45.56.176.27:7605:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>alberodamian90@gmail.com</t>
-  </si>
-  <si>
-    <t>albertodamian90</t>
-  </si>
-  <si>
-    <t>mohamedkazaz88@yahoo.com</t>
-  </si>
-  <si>
-    <t>mohamed46260908</t>
-  </si>
-  <si>
-    <t>rosehardly@yhoo.com</t>
-  </si>
-  <si>
-    <t>rosehardly</t>
+    <t>ghanoustar@facebook.com</t>
+  </si>
+  <si>
+    <t>ghanoustar</t>
+  </si>
+  <si>
+    <t>I9FfP6QLk1Wj7sxJn</t>
+  </si>
+  <si>
+    <t>eemekal@hotmail.com</t>
+  </si>
+  <si>
+    <t>eemekall</t>
+  </si>
+  <si>
+    <t>bcmhwxS50uq3NJed</t>
+  </si>
+  <si>
+    <t>howardjk46@hotmail.com</t>
+  </si>
+  <si>
+    <t>howardjk46</t>
+  </si>
+  <si>
+    <t>qKRNohCVLmk9MWzS</t>
   </si>
   <si>
     <t>72.1.178.194:7088:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>loveseey@live.co.uk</t>
-  </si>
-  <si>
-    <t>jakelovesey</t>
-  </si>
-  <si>
-    <t>jukutkesong@ovi.com</t>
-  </si>
-  <si>
-    <t>mitaaditia</t>
-  </si>
-  <si>
-    <t>patleddy5@gmail.com</t>
-  </si>
-  <si>
-    <t>patleddy5</t>
+    <t>ruzanna0902@mail.ru</t>
+  </si>
+  <si>
+    <t>ruzanna0902</t>
+  </si>
+  <si>
+    <t>lrCjVxgqiI5QBMwb</t>
+  </si>
+  <si>
+    <t>soleprats@gmail.com</t>
+  </si>
+  <si>
+    <t>soleprats</t>
+  </si>
+  <si>
+    <t>ruMyk3ZIGxBL7Y</t>
+  </si>
+  <si>
+    <t>karitos@hotmail.fr</t>
+  </si>
+  <si>
+    <t>karimyacine</t>
+  </si>
+  <si>
+    <t>DnFTrjyB83sCO4cPX</t>
   </si>
   <si>
     <t>72.1.178.231:7125:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>erinbraaton9@gmail.com</t>
-  </si>
-  <si>
-    <t>erinbratton</t>
-  </si>
-  <si>
-    <t>annimeba@gmail.com</t>
-  </si>
-  <si>
-    <t>annimeba</t>
-  </si>
-  <si>
-    <t>calenciamay@yahoo.com</t>
-  </si>
-  <si>
-    <t>calenciamay</t>
-  </si>
-  <si>
-    <t>45.56.176.250:7828:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>ophelie.lamotte@hayoo.fr</t>
-  </si>
-  <si>
-    <t>ophelielamotte</t>
-  </si>
-  <si>
-    <t>anabursac98@gmail.com</t>
-  </si>
-  <si>
-    <t>abursac98</t>
-  </si>
-  <si>
-    <t>www.eliabath@2002.com</t>
-  </si>
-  <si>
-    <t>corbinmckee</t>
-  </si>
-  <si>
-    <t>72.1.178.162:7056:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>zuzum_3mo@hotmail.com</t>
-  </si>
-  <si>
-    <t>kaderozcan</t>
-  </si>
-  <si>
-    <t>mikemarold1974@cox.net</t>
-  </si>
-  <si>
-    <t>mikemarold</t>
-  </si>
-  <si>
-    <t>matikamil1998@gmail.com</t>
-  </si>
-  <si>
-    <t>rayvi988</t>
-  </si>
-  <si>
-    <t>45.56.176.210:7788:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>lina.osfour94@gmail.com</t>
-  </si>
-  <si>
-    <t>linaosfour</t>
-  </si>
-  <si>
-    <t>auradesousa@gmail.com</t>
-  </si>
-  <si>
-    <t>auradesousa</t>
-  </si>
-  <si>
-    <t>hlahatra@gmail.com</t>
-  </si>
-  <si>
-    <t>lahatraharizo</t>
-  </si>
-  <si>
-    <t>45.56.176.53:7631:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>gus.popotito@gmail.com</t>
-  </si>
-  <si>
-    <t>guspopotito</t>
-  </si>
-  <si>
-    <t>kiona.mcneil@yaoo.com</t>
-  </si>
-  <si>
-    <t>kionamcneil</t>
-  </si>
-  <si>
-    <t>abu_syafaat@twitter.com</t>
-  </si>
-  <si>
-    <t>wmyasin</t>
-  </si>
-  <si>
-    <t>72.1.178.77:6971:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>emrahkaravus2011@hotmail.com</t>
-  </si>
-  <si>
-    <t>emrahkaravus</t>
-  </si>
-  <si>
-    <t>indianshivamairan@yahoo.com</t>
-  </si>
-  <si>
-    <t>shivamairan</t>
-  </si>
-  <si>
-    <t>hlophesiviwe@twitter.com</t>
-  </si>
-  <si>
-    <t>hlophesiviwe</t>
-  </si>
-  <si>
-    <t>45.56.176.89:7667:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>deprincess266@gmail.com</t>
-  </si>
-  <si>
-    <t>deprincess266</t>
-  </si>
-  <si>
-    <t>jeanrems@gmail.com</t>
-  </si>
-  <si>
-    <t>jeanrems</t>
   </si>
 </sst>
 </file>
@@ -474,7 +453,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,11 +468,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -501,6 +479,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -988,137 +974,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1128,10 +1114,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1657,7 +1650,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -1687,10 +1680,10 @@
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1701,830 +1694,672 @@
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:4">
       <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:4">
-      <c r="A14" s="6" t="s">
-        <v>33</v>
+      <c r="A14" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>35</v>
+        <v>45</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>35</v>
+        <v>52</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="15" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="18" ht="15" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>42</v>
+        <v>59</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>42</v>
+        <v>62</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>49</v>
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>49</v>
+        <v>69</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" ht="15" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>49</v>
+        <v>72</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="15" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>56</v>
+        <v>75</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="24" ht="15" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>56</v>
+        <v>79</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>56</v>
+        <v>82</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" ht="15" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>63</v>
+        <v>85</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="15" spans="1:4">
       <c r="A27" s="3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>63</v>
+        <v>89</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>63</v>
+        <v>92</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="15" spans="1:4">
       <c r="A29" s="3" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>70</v>
+        <v>95</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="15" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>70</v>
+        <v>99</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="31" ht="15" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>70</v>
+        <v>102</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="32" ht="15" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>77</v>
+        <v>105</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="33" ht="15" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>77</v>
+        <v>109</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="34" ht="15" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>77</v>
+        <v>112</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="35" ht="15" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>84</v>
+        <v>115</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="36" ht="15" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>84</v>
+        <v>119</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="37" ht="15" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>84</v>
+        <v>122</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="38" ht="15" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>91</v>
+        <v>125</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="39" ht="15" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>91</v>
+        <v>129</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="40" ht="15" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>91</v>
+        <v>132</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="41" ht="15" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>98</v>
+        <v>135</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="42" ht="15" spans="1:4">
-      <c r="A42" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>98</v>
-      </c>
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="7"/>
     </row>
     <row r="43" ht="15" spans="1:4">
-      <c r="A43" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>98</v>
-      </c>
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
     </row>
     <row r="44" ht="15" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>105</v>
-      </c>
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" ht="15" spans="1:4">
-      <c r="A45" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>105</v>
-      </c>
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" ht="15" spans="1:4">
-      <c r="A46" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>105</v>
-      </c>
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" ht="15" spans="1:4">
-      <c r="A47" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="A47" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" ht="15" spans="1:4">
-      <c r="A48" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="A48" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" ht="15" spans="1:4">
-      <c r="A49" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" ht="15" spans="1:4">
-      <c r="A50" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>119</v>
-      </c>
+      <c r="A50" s="5"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" ht="15" spans="1:4">
-      <c r="A51" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>119</v>
-      </c>
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" ht="15" spans="1:4">
-      <c r="A52" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>119</v>
-      </c>
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" ht="15" spans="1:4">
-      <c r="A53" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>126</v>
-      </c>
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" ht="15" spans="1:4">
-      <c r="A54" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>126</v>
-      </c>
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" ht="15" spans="1:4">
-      <c r="A55" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>126</v>
-      </c>
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" ht="15" spans="1:4">
-      <c r="A56" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" ht="15" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="A57" s="5"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" ht="15" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" ht="15" spans="1:4">
-      <c r="A59" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>140</v>
-      </c>
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" ht="15" spans="1:4">
-      <c r="A60" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>140</v>
-      </c>
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" ht="15" spans="1:4">
-      <c r="A61" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>140</v>
-      </c>
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="8"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="Asd001122@djt"/>
-    <hyperlink ref="A14" r:id="rId2" display="riazhussain_36@gmil.com"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="265">
   <si>
     <t>email</t>
   </si>
@@ -441,6 +441,387 @@
   </si>
   <si>
     <t>72.1.178.231:7125:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>ella.gevondyan@twitter.ru</t>
+  </si>
+  <si>
+    <t>ellagevondyan</t>
+  </si>
+  <si>
+    <t>Asd001122@djt</t>
+  </si>
+  <si>
+    <t>dafeny@mail.com</t>
+  </si>
+  <si>
+    <t>desireemahone</t>
+  </si>
+  <si>
+    <t>francenag@yahoo.com</t>
+  </si>
+  <si>
+    <t>francenag</t>
+  </si>
+  <si>
+    <t>mcjthoto@yahoo.com</t>
+  </si>
+  <si>
+    <t>mcjthoto</t>
+  </si>
+  <si>
+    <t>nantktlady@gmail.com</t>
+  </si>
+  <si>
+    <t>nantktlady</t>
+  </si>
+  <si>
+    <t>babaa_akdemir12@hotmail.com</t>
+  </si>
+  <si>
+    <t>babaaakdemir12</t>
+  </si>
+  <si>
+    <t>babulijo7@gmail.com</t>
+  </si>
+  <si>
+    <t>lijobabucr</t>
+  </si>
+  <si>
+    <t>akrepali_06@windowslive.com</t>
+  </si>
+  <si>
+    <t>alikr11</t>
+  </si>
+  <si>
+    <t>rachaelbeyor@gmail.com</t>
+  </si>
+  <si>
+    <t>rbeyor28</t>
+  </si>
+  <si>
+    <t>tanvimaan@yahoo.in</t>
+  </si>
+  <si>
+    <t>tanvimaan</t>
+  </si>
+  <si>
+    <t>lewagner1965@gmail.com</t>
+  </si>
+  <si>
+    <t>lewagner1965</t>
+  </si>
+  <si>
+    <t>paullechien@gmail.com</t>
+  </si>
+  <si>
+    <t>paullechien</t>
+  </si>
+  <si>
+    <t>riazhussain_36@gmil.com</t>
+  </si>
+  <si>
+    <t>riazhussain36</t>
+  </si>
+  <si>
+    <t>daniela_chulis@hotmail.com</t>
+  </si>
+  <si>
+    <t>chulis_maria</t>
+  </si>
+  <si>
+    <t>matty_2147@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>matty2147</t>
+  </si>
+  <si>
+    <t>arranyounger90@yahoo.co.uk</t>
+  </si>
+  <si>
+    <t>arranyounger</t>
+  </si>
+  <si>
+    <t>laasecina_17@hotmail.com</t>
+  </si>
+  <si>
+    <t>nallely05j</t>
+  </si>
+  <si>
+    <t>recepkalkavan@gmail.com</t>
+  </si>
+  <si>
+    <t>recepkalkavan</t>
+  </si>
+  <si>
+    <t>korbinian.kraus@live.de</t>
+  </si>
+  <si>
+    <t>korbiniankraus</t>
+  </si>
+  <si>
+    <t>elina.glittmark@hotmail.com</t>
+  </si>
+  <si>
+    <t>elinaglittmark</t>
+  </si>
+  <si>
+    <t>murilolenotti@gmail.com</t>
+  </si>
+  <si>
+    <t>murilolenotti</t>
+  </si>
+  <si>
+    <t>pepe.moto@live.cl</t>
+  </si>
+  <si>
+    <t>pepemoto</t>
+  </si>
+  <si>
+    <t>xokrystinavxo@aim.com</t>
+  </si>
+  <si>
+    <t>kvizard</t>
+  </si>
+  <si>
+    <t>dibernado@naver.com</t>
+  </si>
+  <si>
+    <t>dibernado</t>
+  </si>
+  <si>
+    <t>ibrahimyakuburaji@yahoo.com</t>
+  </si>
+  <si>
+    <t>ibwizkid</t>
+  </si>
+  <si>
+    <t>juniorsimons123@gmail.com</t>
+  </si>
+  <si>
+    <t>juniorsimons123</t>
+  </si>
+  <si>
+    <t>iorirahim@ymail.com</t>
+  </si>
+  <si>
+    <t>iorirahim</t>
+  </si>
+  <si>
+    <t>aungsitun53@mail.com</t>
+  </si>
+  <si>
+    <t>aungsitun</t>
+  </si>
+  <si>
+    <t>niklajj60@mail.ru</t>
+  </si>
+  <si>
+    <t>niklajj60</t>
+  </si>
+  <si>
+    <t>prince_oc2000@hotmail.com</t>
+  </si>
+  <si>
+    <t>princechigbu</t>
+  </si>
+  <si>
+    <t>dalkiel_dark666@hitmail.com</t>
+  </si>
+  <si>
+    <t>dalkieldark666</t>
+  </si>
+  <si>
+    <t>hurbbieirving13@yahoo.co</t>
+  </si>
+  <si>
+    <t>hurbbieirving</t>
+  </si>
+  <si>
+    <t>bilbaina14@gmail.com</t>
+  </si>
+  <si>
+    <t>bilbaina14</t>
+  </si>
+  <si>
+    <t>uak_nhk@rediffmail.com</t>
+  </si>
+  <si>
+    <t>uaknhkvamshi</t>
+  </si>
+  <si>
+    <t>alberodamian90@gmail.com</t>
+  </si>
+  <si>
+    <t>albertodamian90</t>
+  </si>
+  <si>
+    <t>mohamedkazaz88@yahoo.com</t>
+  </si>
+  <si>
+    <t>mohamed46260908</t>
+  </si>
+  <si>
+    <t>rosehardly@yhoo.com</t>
+  </si>
+  <si>
+    <t>rosehardly</t>
+  </si>
+  <si>
+    <t>loveseey@live.co.uk</t>
+  </si>
+  <si>
+    <t>jakelovesey</t>
+  </si>
+  <si>
+    <t>jukutkesong@ovi.com</t>
+  </si>
+  <si>
+    <t>mitaaditia</t>
+  </si>
+  <si>
+    <t>patleddy5@gmail.com</t>
+  </si>
+  <si>
+    <t>patleddy5</t>
+  </si>
+  <si>
+    <t>erinbraaton9@gmail.com</t>
+  </si>
+  <si>
+    <t>erinbratton</t>
+  </si>
+  <si>
+    <t>annimeba@gmail.com</t>
+  </si>
+  <si>
+    <t>annimeba</t>
+  </si>
+  <si>
+    <t>calenciamay@yahoo.com</t>
+  </si>
+  <si>
+    <t>calenciamay</t>
+  </si>
+  <si>
+    <t>45.56.176.250:7828:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>ophelie.lamotte@hayoo.fr</t>
+  </si>
+  <si>
+    <t>ophelielamotte</t>
+  </si>
+  <si>
+    <t>anabursac98@gmail.com</t>
+  </si>
+  <si>
+    <t>abursac98</t>
+  </si>
+  <si>
+    <t>www.eliabath@2002.com</t>
+  </si>
+  <si>
+    <t>corbinmckee</t>
+  </si>
+  <si>
+    <t>72.1.178.162:7056:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>zuzum_3mo@hotmail.com</t>
+  </si>
+  <si>
+    <t>kaderozcan</t>
+  </si>
+  <si>
+    <t>mikemarold1974@cox.net</t>
+  </si>
+  <si>
+    <t>mikemarold</t>
+  </si>
+  <si>
+    <t>matikamil1998@gmail.com</t>
+  </si>
+  <si>
+    <t>rayvi988</t>
+  </si>
+  <si>
+    <t>45.56.176.210:7788:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>lina.osfour94@gmail.com</t>
+  </si>
+  <si>
+    <t>linaosfour</t>
+  </si>
+  <si>
+    <t>auradesousa@gmail.com</t>
+  </si>
+  <si>
+    <t>auradesousa</t>
+  </si>
+  <si>
+    <t>hlahatra@gmail.com</t>
+  </si>
+  <si>
+    <t>lahatraharizo</t>
+  </si>
+  <si>
+    <t>45.56.176.53:7631:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>gus.popotito@gmail.com</t>
+  </si>
+  <si>
+    <t>guspopotito</t>
+  </si>
+  <si>
+    <t>kiona.mcneil@yaoo.com</t>
+  </si>
+  <si>
+    <t>kionamcneil</t>
+  </si>
+  <si>
+    <t>abu_syafaat@twitter.com</t>
+  </si>
+  <si>
+    <t>wmyasin</t>
+  </si>
+  <si>
+    <t>72.1.178.77:6971:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>emrahkaravus2011@hotmail.com</t>
+  </si>
+  <si>
+    <t>emrahkaravus</t>
+  </si>
+  <si>
+    <t>indianshivamairan@yahoo.com</t>
+  </si>
+  <si>
+    <t>shivamairan</t>
+  </si>
+  <si>
+    <t>hlophesiviwe@twitter.com</t>
+  </si>
+  <si>
+    <t>hlophesiviwe</t>
+  </si>
+  <si>
+    <t>45.56.176.89:7667:lfxwowly:2ve2stnj09xk</t>
+  </si>
+  <si>
+    <t>deprincess266@gmail.com</t>
+  </si>
+  <si>
+    <t>deprincess266</t>
+  </si>
+  <si>
+    <t>jeanrems@gmail.com</t>
+  </si>
+  <si>
+    <t>jeanrems</t>
   </si>
 </sst>
 </file>
@@ -453,7 +834,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,13 +847,6 @@
       <color theme="1"/>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -974,133 +1348,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1114,11 +1488,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1650,7 +2024,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -2234,130 +2608,844 @@
       </c>
     </row>
     <row r="42" ht="15" spans="1:4">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
+      <c r="A42" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="43" ht="15" spans="1:4">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
+      <c r="A43" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="44" ht="15" spans="1:4">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
+      <c r="A44" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="45" ht="15" spans="1:4">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
+      <c r="A45" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="46" ht="15" spans="1:4">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
+      <c r="A46" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="47" ht="15" spans="1:4">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
+      <c r="A47" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="48" ht="15" spans="1:4">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
+      <c r="A48" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="49" ht="15" spans="1:4">
-      <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
+      <c r="A49" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="50" ht="15" spans="1:4">
-      <c r="A50" s="5"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
+      <c r="A50" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="51" ht="15" spans="1:4">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
+      <c r="A51" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="52" ht="15" spans="1:4">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="7"/>
+      <c r="A52" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="53" ht="15" spans="1:4">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
+      <c r="A53" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="54" ht="15" spans="1:4">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="7"/>
+      <c r="A54" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="55" ht="15" spans="1:4">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
+      <c r="A55" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="56" ht="15" spans="1:4">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="7"/>
+      <c r="A56" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="57" ht="15" spans="1:4">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="7"/>
+      <c r="A57" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="58" ht="15" spans="1:4">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="7"/>
+      <c r="A58" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="59" ht="15" spans="1:4">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="7"/>
+      <c r="A59" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="60" ht="15" spans="1:4">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="7"/>
+      <c r="A60" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="61" ht="15" spans="1:4">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="7"/>
+      <c r="A61" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="8"/>
+      <c r="A62" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>183</v>
+      </c>
+      <c r="B64" t="s">
+        <v>184</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D64" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" t="s">
+        <v>186</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D67" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>191</v>
+      </c>
+      <c r="B68" t="s">
+        <v>192</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D68" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>193</v>
+      </c>
+      <c r="B69" t="s">
+        <v>194</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D69" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>195</v>
+      </c>
+      <c r="B70" t="s">
+        <v>196</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D70" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>197</v>
+      </c>
+      <c r="B71" t="s">
+        <v>198</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D71" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>199</v>
+      </c>
+      <c r="B72" t="s">
+        <v>200</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D72" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>201</v>
+      </c>
+      <c r="B73" t="s">
+        <v>202</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D73" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>203</v>
+      </c>
+      <c r="B74" t="s">
+        <v>204</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D74" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>205</v>
+      </c>
+      <c r="B75" t="s">
+        <v>206</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D75" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>207</v>
+      </c>
+      <c r="B76" t="s">
+        <v>208</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D76" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>209</v>
+      </c>
+      <c r="B77" t="s">
+        <v>210</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D77" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>211</v>
+      </c>
+      <c r="B78" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D78" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>213</v>
+      </c>
+      <c r="B79" t="s">
+        <v>214</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D79" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>215</v>
+      </c>
+      <c r="B80" t="s">
+        <v>216</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D80" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>217</v>
+      </c>
+      <c r="B81" t="s">
+        <v>218</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D81" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>219</v>
+      </c>
+      <c r="B82" t="s">
+        <v>220</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D82" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>221</v>
+      </c>
+      <c r="B83" t="s">
+        <v>222</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D83" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>223</v>
+      </c>
+      <c r="B84" t="s">
+        <v>224</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D84" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>226</v>
+      </c>
+      <c r="B85" t="s">
+        <v>227</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D85" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>228</v>
+      </c>
+      <c r="B86" t="s">
+        <v>229</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D86" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>230</v>
+      </c>
+      <c r="B87" t="s">
+        <v>231</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>233</v>
+      </c>
+      <c r="B88" t="s">
+        <v>234</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D88" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>235</v>
+      </c>
+      <c r="B89" t="s">
+        <v>236</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D89" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>237</v>
+      </c>
+      <c r="B90" t="s">
+        <v>238</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D90" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>240</v>
+      </c>
+      <c r="B91" t="s">
+        <v>241</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D91" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>242</v>
+      </c>
+      <c r="B92" t="s">
+        <v>243</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D92" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>244</v>
+      </c>
+      <c r="B93" t="s">
+        <v>245</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>247</v>
+      </c>
+      <c r="B94" t="s">
+        <v>248</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D94" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>249</v>
+      </c>
+      <c r="B95" t="s">
+        <v>250</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D95" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>251</v>
+      </c>
+      <c r="B96" t="s">
+        <v>252</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D96" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>254</v>
+      </c>
+      <c r="B97" t="s">
+        <v>255</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D97" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>256</v>
+      </c>
+      <c r="B98" t="s">
+        <v>257</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D98" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>258</v>
+      </c>
+      <c r="B99" t="s">
+        <v>259</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D99" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>261</v>
+      </c>
+      <c r="B100" t="s">
+        <v>262</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D100" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>263</v>
+      </c>
+      <c r="B101" t="s">
+        <v>264</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D101" t="s">
+        <v>260</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="325">
   <si>
     <t>email</t>
   </si>
@@ -822,6 +822,186 @@
   </si>
   <si>
     <t>jeanrems</t>
+  </si>
+  <si>
+    <t>kevinramos1969@regardermail.com</t>
+  </si>
+  <si>
+    <t>ElTavarish</t>
+  </si>
+  <si>
+    <t>o0Y5LWwrQ6uG3g9HD</t>
+  </si>
+  <si>
+    <t>marjoriegrose1925@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>coolsirin</t>
+  </si>
+  <si>
+    <t>tGiPgXT0UxZsC6wMIk</t>
+  </si>
+  <si>
+    <t>anthonysmisek1981@demainmail.com</t>
+  </si>
+  <si>
+    <t>abelindalazo</t>
+  </si>
+  <si>
+    <t>KUZY6cwg9azO3ulM</t>
+  </si>
+  <si>
+    <t>myraloving1940@difficilemail.com</t>
+  </si>
+  <si>
+    <t>aabbyreese</t>
+  </si>
+  <si>
+    <t>XTyzdlL6wSmqGEbo</t>
+  </si>
+  <si>
+    <t>charleskidd1936@regardermail.com</t>
+  </si>
+  <si>
+    <t>devollove9</t>
+  </si>
+  <si>
+    <t>dTt0UejyNhB3AzRk6</t>
+  </si>
+  <si>
+    <t>michelemoore1927@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>kimovich2003</t>
+  </si>
+  <si>
+    <t>BvDrC4nkFbRUMwZueP</t>
+  </si>
+  <si>
+    <t>jamesjones1976@regardermail.com</t>
+  </si>
+  <si>
+    <t>horejahk</t>
+  </si>
+  <si>
+    <t>AYhJgIszxPN9Zv</t>
+  </si>
+  <si>
+    <t>johntaylor1937@difficilemail.com</t>
+  </si>
+  <si>
+    <t>batty2106</t>
+  </si>
+  <si>
+    <t>4ZKIxApEDo180LQ</t>
+  </si>
+  <si>
+    <t>carycaputo1973@demainmail.com</t>
+  </si>
+  <si>
+    <t>gailchep</t>
+  </si>
+  <si>
+    <t>8eMSpOYnA3wZNlr</t>
+  </si>
+  <si>
+    <t>sallygonzalez1958@regardermail.com</t>
+  </si>
+  <si>
+    <t>leraneicheva</t>
+  </si>
+  <si>
+    <t>9YUNGed73kRgqT0A</t>
+  </si>
+  <si>
+    <t>jorgeberry1919@difficilemail.com</t>
+  </si>
+  <si>
+    <t>florentlardeux</t>
+  </si>
+  <si>
+    <t>oGtwJTClibgQZx9P</t>
+  </si>
+  <si>
+    <t>joannawright1933@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>AmandaAbo</t>
+  </si>
+  <si>
+    <t>aKgqxO90DSAfnwRT3H</t>
+  </si>
+  <si>
+    <t>mariebrown1978@demainmail.com</t>
+  </si>
+  <si>
+    <t>rekuucii</t>
+  </si>
+  <si>
+    <t>0XeWLNRvnYqbZH</t>
+  </si>
+  <si>
+    <t>davidhood1931@demainmail.com</t>
+  </si>
+  <si>
+    <t>onoelneves</t>
+  </si>
+  <si>
+    <t>8e5fScGwsCDzIgE</t>
+  </si>
+  <si>
+    <t>mariannejackson1961@regardermail.com</t>
+  </si>
+  <si>
+    <t>joramie26</t>
+  </si>
+  <si>
+    <t>VTIvHgcPa4mM3z</t>
+  </si>
+  <si>
+    <t>latishaselvester1999@difficilemail.com</t>
+  </si>
+  <si>
+    <t>feefeebecker</t>
+  </si>
+  <si>
+    <t>ufGrBQ7xtsTXavO1w</t>
+  </si>
+  <si>
+    <t>alejandrobush1939@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>totalweek</t>
+  </si>
+  <si>
+    <t>HIuzP3l2JgfYGc5m</t>
+  </si>
+  <si>
+    <t>joshuaseidl1965@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>josumont</t>
+  </si>
+  <si>
+    <t>0nYtyO4mXvZ8bIcCT</t>
+  </si>
+  <si>
+    <t>gwendolyndeisher1986@difficilemail.com</t>
+  </si>
+  <si>
+    <t>fcojaviero</t>
+  </si>
+  <si>
+    <t>jo68WuqAvUdVc9I</t>
+  </si>
+  <si>
+    <t>maryreyes1927@regardermail.com</t>
+  </si>
+  <si>
+    <t>agdiemme</t>
+  </si>
+  <si>
+    <t>k8O47TLDiAumMyvFeZ</t>
   </si>
 </sst>
 </file>
@@ -834,7 +1014,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -860,6 +1040,13 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1348,137 +1535,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1499,6 +1686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2024,7 +2212,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -3447,6 +3635,286 @@
         <v>260</v>
       </c>
     </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D102" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D103" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D104" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D105" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D106" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B107" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D107" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D108" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D109" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D110" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D111" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D112" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D113" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D114" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="D115" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="D116" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D117" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="D118" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D119" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D120" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="D121" t="s">
+        <v>239</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="203">
   <si>
     <t>email</t>
   </si>
@@ -443,502 +443,136 @@
     <t>72.1.178.231:7125:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>ella.gevondyan@twitter.ru</t>
-  </si>
-  <si>
-    <t>ellagevondyan</t>
-  </si>
-  <si>
-    <t>Asd001122@djt</t>
-  </si>
-  <si>
-    <t>dafeny@mail.com</t>
-  </si>
-  <si>
-    <t>desireemahone</t>
-  </si>
-  <si>
-    <t>francenag@yahoo.com</t>
-  </si>
-  <si>
-    <t>francenag</t>
-  </si>
-  <si>
-    <t>mcjthoto@yahoo.com</t>
-  </si>
-  <si>
-    <t>mcjthoto</t>
-  </si>
-  <si>
-    <t>nantktlady@gmail.com</t>
-  </si>
-  <si>
-    <t>nantktlady</t>
-  </si>
-  <si>
-    <t>babaa_akdemir12@hotmail.com</t>
-  </si>
-  <si>
-    <t>babaaakdemir12</t>
-  </si>
-  <si>
-    <t>babulijo7@gmail.com</t>
-  </si>
-  <si>
-    <t>lijobabucr</t>
-  </si>
-  <si>
-    <t>akrepali_06@windowslive.com</t>
-  </si>
-  <si>
-    <t>alikr11</t>
-  </si>
-  <si>
-    <t>rachaelbeyor@gmail.com</t>
-  </si>
-  <si>
-    <t>rbeyor28</t>
-  </si>
-  <si>
-    <t>tanvimaan@yahoo.in</t>
-  </si>
-  <si>
-    <t>tanvimaan</t>
-  </si>
-  <si>
-    <t>lewagner1965@gmail.com</t>
-  </si>
-  <si>
-    <t>lewagner1965</t>
-  </si>
-  <si>
-    <t>paullechien@gmail.com</t>
-  </si>
-  <si>
-    <t>paullechien</t>
-  </si>
-  <si>
-    <t>riazhussain_36@gmil.com</t>
-  </si>
-  <si>
-    <t>riazhussain36</t>
-  </si>
-  <si>
-    <t>daniela_chulis@hotmail.com</t>
-  </si>
-  <si>
-    <t>chulis_maria</t>
-  </si>
-  <si>
-    <t>matty_2147@hotmail.com.ar</t>
-  </si>
-  <si>
-    <t>matty2147</t>
-  </si>
-  <si>
-    <t>arranyounger90@yahoo.co.uk</t>
-  </si>
-  <si>
-    <t>arranyounger</t>
-  </si>
-  <si>
-    <t>laasecina_17@hotmail.com</t>
-  </si>
-  <si>
-    <t>nallely05j</t>
-  </si>
-  <si>
-    <t>recepkalkavan@gmail.com</t>
-  </si>
-  <si>
-    <t>recepkalkavan</t>
-  </si>
-  <si>
-    <t>korbinian.kraus@live.de</t>
-  </si>
-  <si>
-    <t>korbiniankraus</t>
-  </si>
-  <si>
-    <t>elina.glittmark@hotmail.com</t>
-  </si>
-  <si>
-    <t>elinaglittmark</t>
-  </si>
-  <si>
-    <t>murilolenotti@gmail.com</t>
-  </si>
-  <si>
-    <t>murilolenotti</t>
-  </si>
-  <si>
-    <t>pepe.moto@live.cl</t>
-  </si>
-  <si>
-    <t>pepemoto</t>
-  </si>
-  <si>
-    <t>xokrystinavxo@aim.com</t>
-  </si>
-  <si>
-    <t>kvizard</t>
-  </si>
-  <si>
-    <t>dibernado@naver.com</t>
-  </si>
-  <si>
-    <t>dibernado</t>
-  </si>
-  <si>
-    <t>ibrahimyakuburaji@yahoo.com</t>
-  </si>
-  <si>
-    <t>ibwizkid</t>
-  </si>
-  <si>
-    <t>juniorsimons123@gmail.com</t>
-  </si>
-  <si>
-    <t>juniorsimons123</t>
-  </si>
-  <si>
-    <t>iorirahim@ymail.com</t>
-  </si>
-  <si>
-    <t>iorirahim</t>
-  </si>
-  <si>
-    <t>aungsitun53@mail.com</t>
-  </si>
-  <si>
-    <t>aungsitun</t>
-  </si>
-  <si>
-    <t>niklajj60@mail.ru</t>
-  </si>
-  <si>
-    <t>niklajj60</t>
-  </si>
-  <si>
-    <t>prince_oc2000@hotmail.com</t>
-  </si>
-  <si>
-    <t>princechigbu</t>
-  </si>
-  <si>
-    <t>dalkiel_dark666@hitmail.com</t>
-  </si>
-  <si>
-    <t>dalkieldark666</t>
-  </si>
-  <si>
-    <t>hurbbieirving13@yahoo.co</t>
-  </si>
-  <si>
-    <t>hurbbieirving</t>
-  </si>
-  <si>
-    <t>bilbaina14@gmail.com</t>
-  </si>
-  <si>
-    <t>bilbaina14</t>
-  </si>
-  <si>
-    <t>uak_nhk@rediffmail.com</t>
-  </si>
-  <si>
-    <t>uaknhkvamshi</t>
-  </si>
-  <si>
-    <t>alberodamian90@gmail.com</t>
-  </si>
-  <si>
-    <t>albertodamian90</t>
-  </si>
-  <si>
-    <t>mohamedkazaz88@yahoo.com</t>
-  </si>
-  <si>
-    <t>mohamed46260908</t>
-  </si>
-  <si>
-    <t>rosehardly@yhoo.com</t>
-  </si>
-  <si>
-    <t>rosehardly</t>
-  </si>
-  <si>
-    <t>loveseey@live.co.uk</t>
-  </si>
-  <si>
-    <t>jakelovesey</t>
-  </si>
-  <si>
-    <t>jukutkesong@ovi.com</t>
-  </si>
-  <si>
-    <t>mitaaditia</t>
-  </si>
-  <si>
-    <t>patleddy5@gmail.com</t>
-  </si>
-  <si>
-    <t>patleddy5</t>
-  </si>
-  <si>
-    <t>erinbraaton9@gmail.com</t>
-  </si>
-  <si>
-    <t>erinbratton</t>
-  </si>
-  <si>
-    <t>annimeba@gmail.com</t>
-  </si>
-  <si>
-    <t>annimeba</t>
-  </si>
-  <si>
-    <t>calenciamay@yahoo.com</t>
-  </si>
-  <si>
-    <t>calenciamay</t>
-  </si>
-  <si>
-    <t>45.56.176.250:7828:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>ophelie.lamotte@hayoo.fr</t>
-  </si>
-  <si>
-    <t>ophelielamotte</t>
-  </si>
-  <si>
-    <t>anabursac98@gmail.com</t>
-  </si>
-  <si>
-    <t>abursac98</t>
-  </si>
-  <si>
-    <t>www.eliabath@2002.com</t>
-  </si>
-  <si>
-    <t>corbinmckee</t>
+    <t>kevinramos1969@regardermail.com</t>
+  </si>
+  <si>
+    <t>ElTavarish</t>
+  </si>
+  <si>
+    <t>o0Y5LWwrQ6uG3g9HD</t>
   </si>
   <si>
     <t>72.1.178.162:7056:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>zuzum_3mo@hotmail.com</t>
-  </si>
-  <si>
-    <t>kaderozcan</t>
-  </si>
-  <si>
-    <t>mikemarold1974@cox.net</t>
-  </si>
-  <si>
-    <t>mikemarold</t>
-  </si>
-  <si>
-    <t>matikamil1998@gmail.com</t>
-  </si>
-  <si>
-    <t>rayvi988</t>
+    <t>marjoriegrose1925@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>coolsirin</t>
+  </si>
+  <si>
+    <t>tGiPgXT0UxZsC6wMIk</t>
+  </si>
+  <si>
+    <t>anthonysmisek1981@demainmail.com</t>
+  </si>
+  <si>
+    <t>abelindalazo</t>
+  </si>
+  <si>
+    <t>KUZY6cwg9azO3ulM</t>
+  </si>
+  <si>
+    <t>myraloving1940@difficilemail.com</t>
+  </si>
+  <si>
+    <t>aabbyreese</t>
+  </si>
+  <si>
+    <t>XTyzdlL6wSmqGEbo</t>
   </si>
   <si>
     <t>45.56.176.210:7788:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>lina.osfour94@gmail.com</t>
-  </si>
-  <si>
-    <t>linaosfour</t>
-  </si>
-  <si>
-    <t>auradesousa@gmail.com</t>
-  </si>
-  <si>
-    <t>auradesousa</t>
-  </si>
-  <si>
-    <t>hlahatra@gmail.com</t>
-  </si>
-  <si>
-    <t>lahatraharizo</t>
+    <t>charleskidd1936@regardermail.com</t>
+  </si>
+  <si>
+    <t>devollove9</t>
+  </si>
+  <si>
+    <t>dTt0UejyNhB3AzRk6</t>
+  </si>
+  <si>
+    <t>michelemoore1927@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>kimovich2003</t>
+  </si>
+  <si>
+    <t>BvDrC4nkFbRUMwZueP</t>
+  </si>
+  <si>
+    <t>jamesjones1976@regardermail.com</t>
+  </si>
+  <si>
+    <t>horejahk</t>
+  </si>
+  <si>
+    <t>AYhJgIszxPN9Zv</t>
   </si>
   <si>
     <t>45.56.176.53:7631:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>gus.popotito@gmail.com</t>
-  </si>
-  <si>
-    <t>guspopotito</t>
-  </si>
-  <si>
-    <t>kiona.mcneil@yaoo.com</t>
-  </si>
-  <si>
-    <t>kionamcneil</t>
-  </si>
-  <si>
-    <t>abu_syafaat@twitter.com</t>
-  </si>
-  <si>
-    <t>wmyasin</t>
+    <t>johntaylor1937@difficilemail.com</t>
+  </si>
+  <si>
+    <t>batty2106</t>
+  </si>
+  <si>
+    <t>4ZKIxApEDo180LQ</t>
+  </si>
+  <si>
+    <t>carycaputo1973@demainmail.com</t>
+  </si>
+  <si>
+    <t>gailchep</t>
+  </si>
+  <si>
+    <t>8eMSpOYnA3wZNlr</t>
+  </si>
+  <si>
+    <t>sallygonzalez1958@regardermail.com</t>
+  </si>
+  <si>
+    <t>leraneicheva</t>
+  </si>
+  <si>
+    <t>9YUNGed73kRgqT0A</t>
   </si>
   <si>
     <t>72.1.178.77:6971:lfxwowly:2ve2stnj09xk</t>
   </si>
   <si>
-    <t>emrahkaravus2011@hotmail.com</t>
-  </si>
-  <si>
-    <t>emrahkaravus</t>
-  </si>
-  <si>
-    <t>indianshivamairan@yahoo.com</t>
-  </si>
-  <si>
-    <t>shivamairan</t>
-  </si>
-  <si>
-    <t>hlophesiviwe@twitter.com</t>
-  </si>
-  <si>
-    <t>hlophesiviwe</t>
+    <t>jorgeberry1919@difficilemail.com</t>
+  </si>
+  <si>
+    <t>florentlardeux</t>
+  </si>
+  <si>
+    <t>oGtwJTClibgQZx9P</t>
+  </si>
+  <si>
+    <t>joannawright1933@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>AmandaAbo</t>
+  </si>
+  <si>
+    <t>aKgqxO90DSAfnwRT3H</t>
+  </si>
+  <si>
+    <t>mariebrown1978@demainmail.com</t>
+  </si>
+  <si>
+    <t>rekuucii</t>
+  </si>
+  <si>
+    <t>0XeWLNRvnYqbZH</t>
   </si>
   <si>
     <t>45.56.176.89:7667:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>deprincess266@gmail.com</t>
-  </si>
-  <si>
-    <t>deprincess266</t>
-  </si>
-  <si>
-    <t>jeanrems@gmail.com</t>
-  </si>
-  <si>
-    <t>jeanrems</t>
-  </si>
-  <si>
-    <t>kevinramos1969@regardermail.com</t>
-  </si>
-  <si>
-    <t>ElTavarish</t>
-  </si>
-  <si>
-    <t>o0Y5LWwrQ6uG3g9HD</t>
-  </si>
-  <si>
-    <t>marjoriegrose1925@utiliseremail.com</t>
-  </si>
-  <si>
-    <t>coolsirin</t>
-  </si>
-  <si>
-    <t>tGiPgXT0UxZsC6wMIk</t>
-  </si>
-  <si>
-    <t>anthonysmisek1981@demainmail.com</t>
-  </si>
-  <si>
-    <t>abelindalazo</t>
-  </si>
-  <si>
-    <t>KUZY6cwg9azO3ulM</t>
-  </si>
-  <si>
-    <t>myraloving1940@difficilemail.com</t>
-  </si>
-  <si>
-    <t>aabbyreese</t>
-  </si>
-  <si>
-    <t>XTyzdlL6wSmqGEbo</t>
-  </si>
-  <si>
-    <t>charleskidd1936@regardermail.com</t>
-  </si>
-  <si>
-    <t>devollove9</t>
-  </si>
-  <si>
-    <t>dTt0UejyNhB3AzRk6</t>
-  </si>
-  <si>
-    <t>michelemoore1927@utiliseremail.com</t>
-  </si>
-  <si>
-    <t>kimovich2003</t>
-  </si>
-  <si>
-    <t>BvDrC4nkFbRUMwZueP</t>
-  </si>
-  <si>
-    <t>jamesjones1976@regardermail.com</t>
-  </si>
-  <si>
-    <t>horejahk</t>
-  </si>
-  <si>
-    <t>AYhJgIszxPN9Zv</t>
-  </si>
-  <si>
-    <t>johntaylor1937@difficilemail.com</t>
-  </si>
-  <si>
-    <t>batty2106</t>
-  </si>
-  <si>
-    <t>4ZKIxApEDo180LQ</t>
-  </si>
-  <si>
-    <t>carycaputo1973@demainmail.com</t>
-  </si>
-  <si>
-    <t>gailchep</t>
-  </si>
-  <si>
-    <t>8eMSpOYnA3wZNlr</t>
-  </si>
-  <si>
-    <t>sallygonzalez1958@regardermail.com</t>
-  </si>
-  <si>
-    <t>leraneicheva</t>
-  </si>
-  <si>
-    <t>9YUNGed73kRgqT0A</t>
-  </si>
-  <si>
-    <t>jorgeberry1919@difficilemail.com</t>
-  </si>
-  <si>
-    <t>florentlardeux</t>
-  </si>
-  <si>
-    <t>oGtwJTClibgQZx9P</t>
-  </si>
-  <si>
-    <t>joannawright1933@utiliseremail.com</t>
-  </si>
-  <si>
-    <t>AmandaAbo</t>
-  </si>
-  <si>
-    <t>aKgqxO90DSAfnwRT3H</t>
-  </si>
-  <si>
-    <t>mariebrown1978@demainmail.com</t>
-  </si>
-  <si>
-    <t>rekuucii</t>
-  </si>
-  <si>
-    <t>0XeWLNRvnYqbZH</t>
   </si>
   <si>
     <t>davidhood1931@demainmail.com</t>
@@ -1014,7 +648,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1033,21 +667,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1535,137 +1154,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1677,16 +1296,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2212,7 +1821,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -2795,1124 +2404,284 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" ht="15" spans="1:4">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:4">
+      <c r="A42" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" ht="15" spans="1:4">
-      <c r="A43" s="5" t="s">
+      <c r="D42" t="s">
         <v>141</v>
       </c>
-      <c r="B43" s="5" t="s">
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" ht="15" spans="1:4">
-      <c r="A44" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C43" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" ht="15" spans="1:4">
-      <c r="A45" s="5" t="s">
+      <c r="D43" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" ht="15" spans="1:4">
-      <c r="A46" s="5" t="s">
+      <c r="C44" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="D44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" ht="15" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C45" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" ht="15" spans="1:4">
-      <c r="A48" s="5" t="s">
+      <c r="D45" t="s">
         <v>151</v>
       </c>
-      <c r="B48" s="5" t="s">
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" ht="15" spans="1:4">
-      <c r="A49" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C46" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" ht="15" spans="1:4">
-      <c r="A50" s="5" t="s">
+      <c r="D46" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" ht="15" spans="1:4">
-      <c r="A51" s="5" t="s">
+      <c r="C47" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="D47" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="52" ht="15" spans="1:4">
-      <c r="A52" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C48" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="53" ht="15" spans="1:4">
-      <c r="A53" s="5" t="s">
+      <c r="D48" t="s">
         <v>161</v>
       </c>
-      <c r="B53" s="5" t="s">
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="54" ht="15" spans="1:4">
-      <c r="A54" s="5" t="s">
+      <c r="B49" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C49" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="55" ht="15" spans="1:4">
-      <c r="A55" s="5" t="s">
+      <c r="D49" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B50" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="56" ht="15" spans="1:4">
-      <c r="A56" s="5" t="s">
+      <c r="C50" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="D50" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="57" ht="15" spans="1:4">
-      <c r="A57" s="5" t="s">
+      <c r="B51" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="C51" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" ht="15" spans="1:4">
-      <c r="A58" s="5" t="s">
+      <c r="D51" t="s">
         <v>171</v>
       </c>
-      <c r="B58" s="5" t="s">
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" ht="15" spans="1:4">
-      <c r="A59" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C52" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" ht="15" spans="1:4">
-      <c r="A60" s="5" t="s">
+      <c r="D52" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="61" ht="15" spans="1:4">
-      <c r="A61" s="5" t="s">
+      <c r="C53" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="D53" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="8" t="s">
+      <c r="B54" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="C54" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" t="s">
+      <c r="D54" t="s">
         <v>181</v>
       </c>
-      <c r="B63" t="s">
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D63" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
+      <c r="B55" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C55" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D64" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
+      <c r="D55" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B56" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D65" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
+      <c r="C56" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B66" t="s">
+      <c r="D56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D66" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
+      <c r="B57" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C57" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D67" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" t="s">
+      <c r="D57" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B58" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D68" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
+      <c r="C58" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D58" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D69" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
+      <c r="B59" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C59" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D70" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
+      <c r="D59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B60" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D71" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
+      <c r="C60" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B72" t="s">
+      <c r="D60" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D72" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" t="s">
+      <c r="B61" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C61" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D73" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" t="s">
-        <v>203</v>
-      </c>
-      <c r="B74" t="s">
-        <v>204</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D74" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
-        <v>205</v>
-      </c>
-      <c r="B75" t="s">
-        <v>206</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D75" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
-        <v>207</v>
-      </c>
-      <c r="B76" t="s">
-        <v>208</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D76" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
-        <v>209</v>
-      </c>
-      <c r="B77" t="s">
-        <v>210</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D77" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
-        <v>211</v>
-      </c>
-      <c r="B78" t="s">
-        <v>212</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D78" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
-        <v>213</v>
-      </c>
-      <c r="B79" t="s">
-        <v>214</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D79" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>215</v>
-      </c>
-      <c r="B80" t="s">
-        <v>216</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D80" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
-        <v>217</v>
-      </c>
-      <c r="B81" t="s">
-        <v>218</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D81" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
-        <v>219</v>
-      </c>
-      <c r="B82" t="s">
-        <v>220</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D82" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
-        <v>221</v>
-      </c>
-      <c r="B83" t="s">
-        <v>222</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D83" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" t="s">
-        <v>223</v>
-      </c>
-      <c r="B84" t="s">
-        <v>224</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D84" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" t="s">
-        <v>226</v>
-      </c>
-      <c r="B85" t="s">
-        <v>227</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D85" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" t="s">
-        <v>228</v>
-      </c>
-      <c r="B86" t="s">
-        <v>229</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D86" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" t="s">
-        <v>230</v>
-      </c>
-      <c r="B87" t="s">
-        <v>231</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D87" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
-        <v>233</v>
-      </c>
-      <c r="B88" t="s">
-        <v>234</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D88" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
-        <v>235</v>
-      </c>
-      <c r="B89" t="s">
-        <v>236</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D89" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
-        <v>237</v>
-      </c>
-      <c r="B90" t="s">
-        <v>238</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D90" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" t="s">
-        <v>240</v>
-      </c>
-      <c r="B91" t="s">
-        <v>241</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D91" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" t="s">
-        <v>242</v>
-      </c>
-      <c r="B92" t="s">
-        <v>243</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D92" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
-        <v>244</v>
-      </c>
-      <c r="B93" t="s">
-        <v>245</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D93" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" t="s">
-        <v>247</v>
-      </c>
-      <c r="B94" t="s">
-        <v>248</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D94" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" t="s">
-        <v>249</v>
-      </c>
-      <c r="B95" t="s">
-        <v>250</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D95" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" t="s">
-        <v>251</v>
-      </c>
-      <c r="B96" t="s">
-        <v>252</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D96" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>254</v>
-      </c>
-      <c r="B97" t="s">
-        <v>255</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D97" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" t="s">
-        <v>256</v>
-      </c>
-      <c r="B98" t="s">
-        <v>257</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D98" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
-        <v>258</v>
-      </c>
-      <c r="B99" t="s">
-        <v>259</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D99" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" t="s">
-        <v>261</v>
-      </c>
-      <c r="B100" t="s">
-        <v>262</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D100" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" t="s">
-        <v>263</v>
-      </c>
-      <c r="B101" t="s">
-        <v>264</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D101" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="B102" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="D102" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="B103" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="C103" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="D103" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B104" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="D104" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="B105" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="D105" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="D106" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="B107" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="D107" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="B108" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="D108" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="D109" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="B110" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="D110" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="B111" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D111" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="D112" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="B113" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D113" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="B114" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="D114" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="B115" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="D115" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="B116" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="D116" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="B117" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="D117" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="D118" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="D119" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="B120" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="D120" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="B121" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="D121" t="s">
-        <v>239</v>
+      <c r="D61" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
   <si>
     <t>email</t>
   </si>
@@ -41,6 +41,9 @@
     <t>residential_proxy</t>
   </si>
   <si>
+    <t>2FA</t>
+  </si>
+  <si>
     <t>moorental@gmail.com</t>
   </si>
   <si>
@@ -441,201 +444,6 @@
   </si>
   <si>
     <t>72.1.178.231:7125:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>kevinramos1969@regardermail.com</t>
-  </si>
-  <si>
-    <t>ElTavarish</t>
-  </si>
-  <si>
-    <t>o0Y5LWwrQ6uG3g9HD</t>
-  </si>
-  <si>
-    <t>72.1.178.162:7056:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>marjoriegrose1925@utiliseremail.com</t>
-  </si>
-  <si>
-    <t>coolsirin</t>
-  </si>
-  <si>
-    <t>tGiPgXT0UxZsC6wMIk</t>
-  </si>
-  <si>
-    <t>anthonysmisek1981@demainmail.com</t>
-  </si>
-  <si>
-    <t>abelindalazo</t>
-  </si>
-  <si>
-    <t>KUZY6cwg9azO3ulM</t>
-  </si>
-  <si>
-    <t>myraloving1940@difficilemail.com</t>
-  </si>
-  <si>
-    <t>aabbyreese</t>
-  </si>
-  <si>
-    <t>XTyzdlL6wSmqGEbo</t>
-  </si>
-  <si>
-    <t>45.56.176.210:7788:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>charleskidd1936@regardermail.com</t>
-  </si>
-  <si>
-    <t>devollove9</t>
-  </si>
-  <si>
-    <t>dTt0UejyNhB3AzRk6</t>
-  </si>
-  <si>
-    <t>michelemoore1927@utiliseremail.com</t>
-  </si>
-  <si>
-    <t>kimovich2003</t>
-  </si>
-  <si>
-    <t>BvDrC4nkFbRUMwZueP</t>
-  </si>
-  <si>
-    <t>jamesjones1976@regardermail.com</t>
-  </si>
-  <si>
-    <t>horejahk</t>
-  </si>
-  <si>
-    <t>AYhJgIszxPN9Zv</t>
-  </si>
-  <si>
-    <t>45.56.176.53:7631:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>johntaylor1937@difficilemail.com</t>
-  </si>
-  <si>
-    <t>batty2106</t>
-  </si>
-  <si>
-    <t>4ZKIxApEDo180LQ</t>
-  </si>
-  <si>
-    <t>carycaputo1973@demainmail.com</t>
-  </si>
-  <si>
-    <t>gailchep</t>
-  </si>
-  <si>
-    <t>8eMSpOYnA3wZNlr</t>
-  </si>
-  <si>
-    <t>sallygonzalez1958@regardermail.com</t>
-  </si>
-  <si>
-    <t>leraneicheva</t>
-  </si>
-  <si>
-    <t>9YUNGed73kRgqT0A</t>
-  </si>
-  <si>
-    <t>72.1.178.77:6971:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>jorgeberry1919@difficilemail.com</t>
-  </si>
-  <si>
-    <t>florentlardeux</t>
-  </si>
-  <si>
-    <t>oGtwJTClibgQZx9P</t>
-  </si>
-  <si>
-    <t>joannawright1933@utiliseremail.com</t>
-  </si>
-  <si>
-    <t>AmandaAbo</t>
-  </si>
-  <si>
-    <t>aKgqxO90DSAfnwRT3H</t>
-  </si>
-  <si>
-    <t>mariebrown1978@demainmail.com</t>
-  </si>
-  <si>
-    <t>rekuucii</t>
-  </si>
-  <si>
-    <t>0XeWLNRvnYqbZH</t>
-  </si>
-  <si>
-    <t>45.56.176.89:7667:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
-    <t>davidhood1931@demainmail.com</t>
-  </si>
-  <si>
-    <t>onoelneves</t>
-  </si>
-  <si>
-    <t>8e5fScGwsCDzIgE</t>
-  </si>
-  <si>
-    <t>mariannejackson1961@regardermail.com</t>
-  </si>
-  <si>
-    <t>joramie26</t>
-  </si>
-  <si>
-    <t>VTIvHgcPa4mM3z</t>
-  </si>
-  <si>
-    <t>latishaselvester1999@difficilemail.com</t>
-  </si>
-  <si>
-    <t>feefeebecker</t>
-  </si>
-  <si>
-    <t>ufGrBQ7xtsTXavO1w</t>
-  </si>
-  <si>
-    <t>alejandrobush1939@utiliseremail.com</t>
-  </si>
-  <si>
-    <t>totalweek</t>
-  </si>
-  <si>
-    <t>HIuzP3l2JgfYGc5m</t>
-  </si>
-  <si>
-    <t>joshuaseidl1965@utiliseremail.com</t>
-  </si>
-  <si>
-    <t>josumont</t>
-  </si>
-  <si>
-    <t>0nYtyO4mXvZ8bIcCT</t>
-  </si>
-  <si>
-    <t>gwendolyndeisher1986@difficilemail.com</t>
-  </si>
-  <si>
-    <t>fcojaviero</t>
-  </si>
-  <si>
-    <t>jo68WuqAvUdVc9I</t>
-  </si>
-  <si>
-    <t>maryreyes1927@regardermail.com</t>
-  </si>
-  <si>
-    <t>agdiemme</t>
-  </si>
-  <si>
-    <t>k8O47TLDiAumMyvFeZ</t>
   </si>
 </sst>
 </file>
@@ -1821,16 +1629,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
     <col min="2" max="2" width="20.3583333333333" customWidth="1"/>
     <col min="3" max="3" width="21.3166666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="43.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="43.9666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39" customHeight="1" spans="1:4">
+    <row r="1" ht="39" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1843,845 +1652,568 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" ht="15" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:4">
       <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:4">
       <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:4">
       <c r="A9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:4">
       <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="15" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" ht="15" spans="1:4">
       <c r="A15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" ht="15" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="15" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" ht="15" spans="1:4">
       <c r="A18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="19" ht="15" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="15" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:4">
       <c r="A21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="22" ht="15" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" ht="15" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" ht="15" spans="1:4">
       <c r="A24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="25" ht="15" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" ht="15" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" ht="15" spans="1:4">
       <c r="A27" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" ht="15" spans="1:4">
       <c r="A29" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" ht="15" spans="1:4">
       <c r="A30" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="31" ht="15" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" ht="15" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" ht="15" spans="1:4">
       <c r="A33" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="34" ht="15" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" ht="15" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" ht="15" spans="1:4">
       <c r="A36" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="37" ht="15" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" ht="15" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" ht="15" spans="1:4">
       <c r="A39" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="40" ht="15" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" ht="15" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D43" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D45" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D46" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D47" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D48" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D49" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D50" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D51" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D52" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D53" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D54" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D55" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D56" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D57" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D58" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D60" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D61" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
   <si>
     <t>email</t>
   </si>
@@ -38,12 +38,12 @@
     <t>password</t>
   </si>
   <si>
+    <t>totp_secret</t>
+  </si>
+  <si>
     <t>residential_proxy</t>
   </si>
   <si>
-    <t>2FA</t>
-  </si>
-  <si>
     <t>moorental@gmail.com</t>
   </si>
   <si>
@@ -53,9 +53,6 @@
     <t>Y5bIKueZX7CVtlp</t>
   </si>
   <si>
-    <t>45.56.176.128:7706:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>miguelmac1986@hotnail.com</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>r6yhjbdwZNFuMPR1V</t>
   </si>
   <si>
-    <t>45.56.176.3:7581:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>randy-2009@live.fr</t>
   </si>
   <si>
@@ -113,9 +107,6 @@
     <t>WM5s34HGuSzh9D</t>
   </si>
   <si>
-    <t>72.1.178.176:7070:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>taytu1704@gmail.com</t>
   </si>
   <si>
@@ -143,9 +134,6 @@
     <t>0HNejaOUqXrCRD</t>
   </si>
   <si>
-    <t>45.56.176.73:7651:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>codey09@hotmail.com</t>
   </si>
   <si>
@@ -173,9 +161,6 @@
     <t>ktBrRwuyvb2ljeITZ8</t>
   </si>
   <si>
-    <t>72.1.178.209:7103:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>sonu.rajput60@yahoo.in</t>
   </si>
   <si>
@@ -203,9 +188,6 @@
     <t>jTfWyGJMvhbISduD5</t>
   </si>
   <si>
-    <t>72.1.178.26:6920:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>cianabanana@icloud.com</t>
   </si>
   <si>
@@ -233,9 +215,6 @@
     <t>BGoORDnmeQWJTEp</t>
   </si>
   <si>
-    <t>45.56.176.224:7802:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>cdavid2489@gmail.com</t>
   </si>
   <si>
@@ -263,9 +242,6 @@
     <t>6QZ3emxE5AN8K1HU9q</t>
   </si>
   <si>
-    <t>45.56.176.227:7805:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>memo.hope.sy@hotmail.com</t>
   </si>
   <si>
@@ -293,9 +269,6 @@
     <t>bN2wLxPjGVWB1diu</t>
   </si>
   <si>
-    <t>72.1.178.115:7009:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>willams_gatinho13@hotmail.com</t>
   </si>
   <si>
@@ -323,9 +296,6 @@
     <t>uhxICKAzwpO5DV0</t>
   </si>
   <si>
-    <t>45.56.176.240:7818:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>ofwallace@gmail.com</t>
   </si>
   <si>
@@ -353,9 +323,6 @@
     <t>ZY5rs7IXAHRUtxQae</t>
   </si>
   <si>
-    <t>72.1.178.183:7077:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>mlgerloff@gmail.com</t>
   </si>
   <si>
@@ -383,9 +350,6 @@
     <t>Xrn7jvilSquhTO</t>
   </si>
   <si>
-    <t>45.56.176.27:7605:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>ghanoustar@facebook.com</t>
   </si>
   <si>
@@ -413,9 +377,6 @@
     <t>qKRNohCVLmk9MWzS</t>
   </si>
   <si>
-    <t>72.1.178.194:7088:lfxwowly:2ve2stnj09xk</t>
-  </si>
-  <si>
     <t>ruzanna0902@mail.ru</t>
   </si>
   <si>
@@ -443,7 +404,244 @@
     <t>DnFTrjyB83sCO4cPX</t>
   </si>
   <si>
-    <t>72.1.178.231:7125:lfxwowly:2ve2stnj09xk</t>
+    <t>kevinramos1969@regardermail.com</t>
+  </si>
+  <si>
+    <t>ElTavarish</t>
+  </si>
+  <si>
+    <t>o0Y5LWwrQ6uG3g9HD</t>
+  </si>
+  <si>
+    <t>KHFTY63TIAIPEBBY</t>
+  </si>
+  <si>
+    <t>marjoriegrose1925@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>coolsirin</t>
+  </si>
+  <si>
+    <t>tGiPgXT0UxZsC6wMIk</t>
+  </si>
+  <si>
+    <t>65PQKQVFUZRNSJ7P</t>
+  </si>
+  <si>
+    <t>anthonysmisek1981@demainmail.com</t>
+  </si>
+  <si>
+    <t>abelindalazo</t>
+  </si>
+  <si>
+    <t>KUZY6cwg9azO3ulM</t>
+  </si>
+  <si>
+    <t>OK7VGFBM7MJPB6M4</t>
+  </si>
+  <si>
+    <t>myraloving1940@difficilemail.com</t>
+  </si>
+  <si>
+    <t>aabbyreese</t>
+  </si>
+  <si>
+    <t>XTyzdlL6wSmqGEbo</t>
+  </si>
+  <si>
+    <t>4HRDAZGZC3GNYE2G</t>
+  </si>
+  <si>
+    <t>charleskidd1936@regardermail.com</t>
+  </si>
+  <si>
+    <t>devollove9</t>
+  </si>
+  <si>
+    <t>dTt0UejyNhB3AzRk6</t>
+  </si>
+  <si>
+    <t>3TDG5OAFZWX7BR5O</t>
+  </si>
+  <si>
+    <t>michelemoore1927@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>kimovich2003</t>
+  </si>
+  <si>
+    <t>BvDrC4nkFbRUMwZueP</t>
+  </si>
+  <si>
+    <t>PMY3XG7R2HWJLEFZ</t>
+  </si>
+  <si>
+    <t>jamesjones1976@regardermail.com</t>
+  </si>
+  <si>
+    <t>horejahk</t>
+  </si>
+  <si>
+    <t>AYhJgIszxPN9Zv</t>
+  </si>
+  <si>
+    <t>DOTHZZF3SHJACXFU</t>
+  </si>
+  <si>
+    <t>johntaylor1937@difficilemail.com</t>
+  </si>
+  <si>
+    <t>batty2106</t>
+  </si>
+  <si>
+    <t>4ZKIxApEDo180LQ</t>
+  </si>
+  <si>
+    <t>SILMDIEIWZFJKIWX</t>
+  </si>
+  <si>
+    <t>carycaputo1973@demainmail.com</t>
+  </si>
+  <si>
+    <t>gailchep</t>
+  </si>
+  <si>
+    <t>8eMSpOYnA3wZNlr</t>
+  </si>
+  <si>
+    <t>UTZ6G7Y2TXN2QRPM</t>
+  </si>
+  <si>
+    <t>sallygonzalez1958@regardermail.com</t>
+  </si>
+  <si>
+    <t>leraneicheva</t>
+  </si>
+  <si>
+    <t>9YUNGed73kRgqT0A</t>
+  </si>
+  <si>
+    <t>NQ2YSICJBDKIUHZH</t>
+  </si>
+  <si>
+    <t>jorgeberry1919@difficilemail.com</t>
+  </si>
+  <si>
+    <t>florentlardeux</t>
+  </si>
+  <si>
+    <t>oGtwJTClibgQZx9P</t>
+  </si>
+  <si>
+    <t>RBFLVM6JYVSPO74L</t>
+  </si>
+  <si>
+    <t>joannawright1933@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>AmandaAbo</t>
+  </si>
+  <si>
+    <t>aKgqxO90DSAfnwRT3H</t>
+  </si>
+  <si>
+    <t>7LAQ4XFITD34RBAY</t>
+  </si>
+  <si>
+    <t>mariebrown1978@demainmail.com</t>
+  </si>
+  <si>
+    <t>rekuucii</t>
+  </si>
+  <si>
+    <t>0XeWLNRvnYqbZH</t>
+  </si>
+  <si>
+    <t>7EFFZCJCW7F6RI6D</t>
+  </si>
+  <si>
+    <t>davidhood1931@demainmail.com</t>
+  </si>
+  <si>
+    <t>onoelneves</t>
+  </si>
+  <si>
+    <t>8e5fScGwsCDzIgE</t>
+  </si>
+  <si>
+    <t>LZHWTEVL5SIVSVUP</t>
+  </si>
+  <si>
+    <t>mariannejackson1961@regardermail.com</t>
+  </si>
+  <si>
+    <t>joramie26</t>
+  </si>
+  <si>
+    <t>VTIvHgcPa4mM3z</t>
+  </si>
+  <si>
+    <t>NPOZOZM3OGQZKMRX</t>
+  </si>
+  <si>
+    <t>latishaselvester1999@difficilemail.com</t>
+  </si>
+  <si>
+    <t>feefeebecker</t>
+  </si>
+  <si>
+    <t>ufGrBQ7xtsTXavO1w</t>
+  </si>
+  <si>
+    <t>TUQFDYACBAR6Q4QT</t>
+  </si>
+  <si>
+    <t>alejandrobush1939@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>totalweek</t>
+  </si>
+  <si>
+    <t>HIuzP3l2JgfYGc5m</t>
+  </si>
+  <si>
+    <t>U3FIUCDJHF432UMH</t>
+  </si>
+  <si>
+    <t>joshuaseidl1965@utiliseremail.com</t>
+  </si>
+  <si>
+    <t>josumont</t>
+  </si>
+  <si>
+    <t>0nYtyO4mXvZ8bIcCT</t>
+  </si>
+  <si>
+    <t>72APA66MMTRRDARQ</t>
+  </si>
+  <si>
+    <t>gwendolyndeisher1986@difficilemail.com</t>
+  </si>
+  <si>
+    <t>fcojaviero</t>
+  </si>
+  <si>
+    <t>jo68WuqAvUdVc9I</t>
+  </si>
+  <si>
+    <t>APUTTISCUAW7FPIU</t>
+  </si>
+  <si>
+    <t>maryreyes1927@regardermail.com</t>
+  </si>
+  <si>
+    <t>agdiemme</t>
+  </si>
+  <si>
+    <t>k8O47TLDiAumMyvFeZ</t>
+  </si>
+  <si>
+    <t>RUW7DFCD3IHCIYDL</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1827,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -1666,554 +1864,754 @@
       <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" ht="15" spans="1:4">
       <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" ht="15" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" ht="15" spans="1:4">
       <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" ht="15" spans="1:4">
       <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" ht="15" spans="1:4">
       <c r="A7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" ht="15" spans="1:4">
       <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" ht="15" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" ht="15" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>28</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" ht="15" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" ht="15" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" ht="15" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" ht="15" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" ht="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" ht="15" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" ht="15" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D17" s="4"/>
     </row>
     <row r="18" ht="15" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" ht="15" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="4" t="s">
         <v>58</v>
       </c>
+      <c r="D19" s="4"/>
     </row>
     <row r="20" ht="15" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" ht="15" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D21" s="4"/>
     </row>
     <row r="22" ht="15" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D22" s="4"/>
     </row>
     <row r="23" ht="15" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" ht="15" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" ht="15" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" ht="15" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>88</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" ht="15" spans="1:4">
       <c r="A27" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>88</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" ht="15" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>88</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" ht="15" spans="1:4">
       <c r="A29" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>98</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" ht="15" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>98</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" ht="15" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>98</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" ht="15" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>108</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D32" s="4"/>
     </row>
     <row r="33" ht="15" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>108</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" ht="15" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>108</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" ht="15" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>118</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D35" s="4"/>
     </row>
     <row r="36" ht="15" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>118</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D36" s="4"/>
     </row>
     <row r="37" ht="15" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>118</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D37" s="4"/>
     </row>
     <row r="38" ht="15" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>128</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D38" s="4"/>
     </row>
     <row r="39" ht="15" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>128</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D39" s="4"/>
     </row>
     <row r="40" ht="15" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>128</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D40" s="4"/>
     </row>
     <row r="41" ht="15" spans="1:4">
       <c r="A41" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="4"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="D44" t="s">
         <v>136</v>
       </c>
-      <c r="C41" s="3" t="s">
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
         <v>137</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="B45" t="s">
         <v>138</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D46" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>157</v>
+      </c>
+      <c r="B50" t="s">
+        <v>158</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>161</v>
+      </c>
+      <c r="B51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D51" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D52" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D53" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>173</v>
+      </c>
+      <c r="B54" t="s">
+        <v>174</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D54" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="B55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>181</v>
+      </c>
+      <c r="B56" t="s">
+        <v>182</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D58" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" t="s">
+        <v>194</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>197</v>
+      </c>
+      <c r="B60" t="s">
+        <v>198</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D60" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" t="s">
+        <v>202</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D61" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
   <si>
     <t>email</t>
   </si>
@@ -642,6 +642,306 @@
   </si>
   <si>
     <t>RUW7DFCD3IHCIYDL</t>
+  </si>
+  <si>
+    <t>947_Chase@emailprom.com</t>
+  </si>
+  <si>
+    <t>ChasePope230196</t>
+  </si>
+  <si>
+    <t>xaXchLe86oB</t>
+  </si>
+  <si>
+    <t>IIP4XEXXEL2YJD6V</t>
+  </si>
+  <si>
+    <t>MarioShaw@thmail.org</t>
+  </si>
+  <si>
+    <t>MarioShaw218182</t>
+  </si>
+  <si>
+    <t>KF3cJpUP3hZc</t>
+  </si>
+  <si>
+    <t>PNS6KY3GE3RDDIOB</t>
+  </si>
+  <si>
+    <t>1997__Woods@evangel6.net</t>
+  </si>
+  <si>
+    <t>WoodsTiffa25032</t>
+  </si>
+  <si>
+    <t>07RduY82eaeWE</t>
+  </si>
+  <si>
+    <t>DNK67BVOMJTDQLYX</t>
+  </si>
+  <si>
+    <t>914Ashley@aurummail.life</t>
+  </si>
+  <si>
+    <t>MarieAshle38741</t>
+  </si>
+  <si>
+    <t>T9QDYxnRTViQO</t>
+  </si>
+  <si>
+    <t>OCOVENBCRRQUQB6L</t>
+  </si>
+  <si>
+    <t>Kim__1997@nudgabox.com</t>
+  </si>
+  <si>
+    <t>AmberKim677848</t>
+  </si>
+  <si>
+    <t>y5hqkJzv9S</t>
+  </si>
+  <si>
+    <t>WK6V7WROU77NW76B</t>
+  </si>
+  <si>
+    <t>LindsayYates@notprivatemail.com</t>
+  </si>
+  <si>
+    <t>LindsayYat27776</t>
+  </si>
+  <si>
+    <t>d6evKQl3z</t>
+  </si>
+  <si>
+    <t>4K3TQWAF3YBAS6G5</t>
+  </si>
+  <si>
+    <t>2006__Lane@scribemail.org</t>
+  </si>
+  <si>
+    <t>DavidLane188691</t>
+  </si>
+  <si>
+    <t>GS7SSf6xsf9</t>
+  </si>
+  <si>
+    <t>T2MEJH7JXICUBCSO</t>
+  </si>
+  <si>
+    <t>Manning865@aolsurf.com</t>
+  </si>
+  <si>
+    <t>SamuelMann94202</t>
+  </si>
+  <si>
+    <t>5gGr8chZK8n1g8</t>
+  </si>
+  <si>
+    <t>5HHND5ZF5A3VKLAC</t>
+  </si>
+  <si>
+    <t>Bailey1983@lepostal.net</t>
+  </si>
+  <si>
+    <t>juan_baile10902</t>
+  </si>
+  <si>
+    <t>idyzkZwA06</t>
+  </si>
+  <si>
+    <t>EWG4BTAZWVMFLSF6</t>
+  </si>
+  <si>
+    <t>Vicki1995@bizesmail.net</t>
+  </si>
+  <si>
+    <t>VickiHolla6177</t>
+  </si>
+  <si>
+    <t>jyqRGQ25Kw</t>
+  </si>
+  <si>
+    <t>7BXP6CNI4R3TGLAF</t>
+  </si>
+  <si>
+    <t>yksjbarm@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>AnishDate</t>
+  </si>
+  <si>
+    <t>f8VWbHXrpS</t>
+  </si>
+  <si>
+    <t>UFJVHDG2JXBI6ASP</t>
+  </si>
+  <si>
+    <t>fmpfhkbx@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>girardcyprien</t>
+  </si>
+  <si>
+    <t>t6mYxvggic</t>
+  </si>
+  <si>
+    <t>4342CX7OOO6UXX5I</t>
+  </si>
+  <si>
+    <t>atwkdycj@bientotmail.com</t>
+  </si>
+  <si>
+    <t>koreanskipop</t>
+  </si>
+  <si>
+    <t>sLpQJaWAXT</t>
+  </si>
+  <si>
+    <t>HPCDEOKOAWQRBOHB</t>
+  </si>
+  <si>
+    <t>kqbgucpj@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>jessicalouisek1</t>
+  </si>
+  <si>
+    <t>GYGdJ4hGVw</t>
+  </si>
+  <si>
+    <t>BOLHLXYZRGK6OEQF</t>
+  </si>
+  <si>
+    <t>cbuhbule@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>AdmUniverso</t>
+  </si>
+  <si>
+    <t>n9tA5gJyMQ</t>
+  </si>
+  <si>
+    <t>EF66URDSAKMJE6XI</t>
+  </si>
+  <si>
+    <t>yhgxltvw@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>Diogo_Miguel_20</t>
+  </si>
+  <si>
+    <t>BgtcXwEYGX</t>
+  </si>
+  <si>
+    <t>DGAJGX6YXMCKSRNP</t>
+  </si>
+  <si>
+    <t>edpxabsw@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>vkovpak2014</t>
+  </si>
+  <si>
+    <t>K5nXiHeb59</t>
+  </si>
+  <si>
+    <t>3IEGIWLZB4TBETMZ</t>
+  </si>
+  <si>
+    <t>bnqbnvsd@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>mamawshepherd</t>
+  </si>
+  <si>
+    <t>JTJhiXhAhV</t>
+  </si>
+  <si>
+    <t>Z6AWPXBKBRZ3TJMD</t>
+  </si>
+  <si>
+    <t>imwiqxbo@bientotmail.com</t>
+  </si>
+  <si>
+    <t>walletIncPty</t>
+  </si>
+  <si>
+    <t>m6YY6jfrLx</t>
+  </si>
+  <si>
+    <t>UZVK5BR6LMNBO6F4</t>
+  </si>
+  <si>
+    <t>sxlxqbmo@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>Netoo_2011</t>
+  </si>
+  <si>
+    <t>4wv4keEgng</t>
+  </si>
+  <si>
+    <t>LE6QJNVWDZEFHUVO</t>
+  </si>
+  <si>
+    <t>xztaugvf@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>JRDavis262</t>
+  </si>
+  <si>
+    <t>inh2SeiG5i</t>
+  </si>
+  <si>
+    <t>C4TTBD2W5RNUJSRZ</t>
+  </si>
+  <si>
+    <t>efhzginx@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>gtalty33</t>
+  </si>
+  <si>
+    <t>pCf2jA5KPc</t>
+  </si>
+  <si>
+    <t>MXDGSLAP3FRRXQ7J</t>
+  </si>
+  <si>
+    <t>aeyrkfee@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>arturo4171</t>
+  </si>
+  <si>
+    <t>MvJe2xsYuU</t>
+  </si>
+  <si>
+    <t>A4BPR4UGX6DD4MJZ</t>
+  </si>
+  <si>
+    <t>dnlqamvv@bientotmail.com</t>
+  </si>
+  <si>
+    <t>you_da_only_one</t>
+  </si>
+  <si>
+    <t>Zffah2v8PK</t>
+  </si>
+  <si>
+    <t>X55BROCUXSZC7QSV</t>
+  </si>
+  <si>
+    <t>vixkxsqt@bientotmail.com</t>
+  </si>
+  <si>
+    <t>nocalgirlie</t>
+  </si>
+  <si>
+    <t>TETjesdun8</t>
+  </si>
+  <si>
+    <t>HYOTSEDSIKVIZQKE</t>
   </si>
 </sst>
 </file>
@@ -654,7 +954,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -673,6 +973,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1160,137 +1467,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1302,6 +1609,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1827,7 +2135,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -2614,6 +2922,356 @@
         <v>204</v>
       </c>
     </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26475" windowHeight="12300"/>
+    <workbookView windowWidth="27810" windowHeight="13470"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="445">
   <si>
     <t>email</t>
   </si>
@@ -942,6 +942,426 @@
   </si>
   <si>
     <t>HYOTSEDSIKVIZQKE</t>
+  </si>
+  <si>
+    <t>xxvmsrhw@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>AIK_89545QSS54</t>
+  </si>
+  <si>
+    <t>HwtQFJumEYcjWI</t>
+  </si>
+  <si>
+    <t>IVFGDZKIVIZB3TCR</t>
+  </si>
+  <si>
+    <t>auccnxde@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>soulpureee</t>
+  </si>
+  <si>
+    <t>AXp0d8sLlVtYK5D</t>
+  </si>
+  <si>
+    <t>5HDRFFYJ72F3YSJX</t>
+  </si>
+  <si>
+    <t>xlnpcjdm@bientotmail.com</t>
+  </si>
+  <si>
+    <t>Frank86274819</t>
+  </si>
+  <si>
+    <t>noeYMshc2f9gijNI</t>
+  </si>
+  <si>
+    <t>VUBIKYSPVV23F4ZO</t>
+  </si>
+  <si>
+    <t>egloriph@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>bob78509103</t>
+  </si>
+  <si>
+    <t>pfr57WS3tOnBaHzG</t>
+  </si>
+  <si>
+    <t>FPWKDLJDWXDJJ5A3</t>
+  </si>
+  <si>
+    <t>menovcso@bientotmail.com</t>
+  </si>
+  <si>
+    <t>bgtndolly</t>
+  </si>
+  <si>
+    <t>6ixedZNvVE1urDI</t>
+  </si>
+  <si>
+    <t>N2ETWQX7372NPPDE</t>
+  </si>
+  <si>
+    <t>aqtpgywo@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>priscillaaline1</t>
+  </si>
+  <si>
+    <t>yjzOI3c0YtBLTopx</t>
+  </si>
+  <si>
+    <t>OFMZ6SD6BDDSXRYN</t>
+  </si>
+  <si>
+    <t>xipplxwt@bientotmail.com</t>
+  </si>
+  <si>
+    <t>26f03499b900430</t>
+  </si>
+  <si>
+    <t>iEobnRL90G2Q8A</t>
+  </si>
+  <si>
+    <t>7ID73RRCP5VO2352</t>
+  </si>
+  <si>
+    <t>ljysrivk@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>evivarq</t>
+  </si>
+  <si>
+    <t>Rc2wzLdbhPATIrBn7</t>
+  </si>
+  <si>
+    <t>R2NOI5PKJ3F2PMZK</t>
+  </si>
+  <si>
+    <t>dafcgzvz@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>Bilalmalik316</t>
+  </si>
+  <si>
+    <t>sDvw0WjJep1BMIP</t>
+  </si>
+  <si>
+    <t>AUHF5XUOEQOMHABR</t>
+  </si>
+  <si>
+    <t>pqkktqcl@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>ards6</t>
+  </si>
+  <si>
+    <t>g4C2Pno3hA8SKXtr</t>
+  </si>
+  <si>
+    <t>SYWMPBK3N5DYIATX</t>
+  </si>
+  <si>
+    <t>ifwvjnrv@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>pedrojesse1</t>
+  </si>
+  <si>
+    <t>wmn5JYQq0xLAWdh</t>
+  </si>
+  <si>
+    <t>37YPJDX64GMNLC2Z</t>
+  </si>
+  <si>
+    <t>zjgpquwm@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>hoangpnvtin</t>
+  </si>
+  <si>
+    <t>5CBklAt9cnJ68MxR3a</t>
+  </si>
+  <si>
+    <t>VIMMBKKSIP4QY242</t>
+  </si>
+  <si>
+    <t>dmvjbqhw@bientotmail.com</t>
+  </si>
+  <si>
+    <t>djplaytrack</t>
+  </si>
+  <si>
+    <t>LVlud2gQIFxXUsCP</t>
+  </si>
+  <si>
+    <t>WF4E3GZBHWAL64UZ</t>
+  </si>
+  <si>
+    <t>drxvgnvm@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>alfonso96salin1</t>
+  </si>
+  <si>
+    <t>bOny0CJB1Pjp8M5cre</t>
+  </si>
+  <si>
+    <t>7BCUFOFQ757TMZC2</t>
+  </si>
+  <si>
+    <t>ygmrythp@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>Denya26761020</t>
+  </si>
+  <si>
+    <t>sLoz6Tb0dYvrQnVZ7E</t>
+  </si>
+  <si>
+    <t>LBJNKMYT3L3QIUYQ</t>
+  </si>
+  <si>
+    <t>aycwtvkd@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>DivyaKa22892011</t>
+  </si>
+  <si>
+    <t>HwTIQ813pfKiycW6a</t>
+  </si>
+  <si>
+    <t>GXOHSZQ6AQCOPTF2</t>
+  </si>
+  <si>
+    <t>qynnxydn@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>CaitlynAzzopar1</t>
+  </si>
+  <si>
+    <t>Bsby6MmzoijZrCx8lW</t>
+  </si>
+  <si>
+    <t>ZJU6CIR5RKDOZKSV</t>
+  </si>
+  <si>
+    <t>wkngzbtk@bientotmail.com</t>
+  </si>
+  <si>
+    <t>tmtzbeyond</t>
+  </si>
+  <si>
+    <t>C8EbAe7qszQBIPf</t>
+  </si>
+  <si>
+    <t>SP7GFEK5W57UALLP</t>
+  </si>
+  <si>
+    <t>dxvvbadv@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>shannon241971</t>
+  </si>
+  <si>
+    <t>9GdC15AO4Ku73xB</t>
+  </si>
+  <si>
+    <t>47QJPKXAUCLH6PDD</t>
+  </si>
+  <si>
+    <t>seqpzckj@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>javierblanco19</t>
+  </si>
+  <si>
+    <t>bgFMEQ3Xa9tAYhdVm</t>
+  </si>
+  <si>
+    <t>2MI43S7I6HK253GQ</t>
+  </si>
+  <si>
+    <t>ofjhacbn@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>pretimbolado1</t>
+  </si>
+  <si>
+    <t>uIU46oDJqdsk0SlBKE</t>
+  </si>
+  <si>
+    <t>X3MYNNG7F2TZ2TSL</t>
+  </si>
+  <si>
+    <t>tmmnvwkq@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>YecinAchek</t>
+  </si>
+  <si>
+    <t>2SeN9K3EUGYXTI</t>
+  </si>
+  <si>
+    <t>QTQ3OQOSWSLNPWTT</t>
+  </si>
+  <si>
+    <t>rkfxoobk@bientotmail.com</t>
+  </si>
+  <si>
+    <t>dolorescursocan</t>
+  </si>
+  <si>
+    <t>mQyhX3PG4jYLORdc</t>
+  </si>
+  <si>
+    <t>T3RPB3X4Q7TC4CMV</t>
+  </si>
+  <si>
+    <t>zmurjkxv@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>umehiroda</t>
+  </si>
+  <si>
+    <t>6KhaE7wbNpmBjC1OYk</t>
+  </si>
+  <si>
+    <t>WG3IWLXKFCHVNNJQ</t>
+  </si>
+  <si>
+    <t>pndmsoqw@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>dimplez2dope</t>
+  </si>
+  <si>
+    <t>siS8JuG65cDn3EVo</t>
+  </si>
+  <si>
+    <t>OGOOADB47IJ7C65L</t>
+  </si>
+  <si>
+    <t>xbrnblmu@bientotmail.com</t>
+  </si>
+  <si>
+    <t>louisgrrr</t>
+  </si>
+  <si>
+    <t>pCwrseHgnSOM0dq</t>
+  </si>
+  <si>
+    <t>BU4UUHNZNDABZX3O</t>
+  </si>
+  <si>
+    <t>zxvixpan@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>AydansMommii</t>
+  </si>
+  <si>
+    <t>EjnwuNJBL37WGoCc</t>
+  </si>
+  <si>
+    <t>2WEBBIPOASMMPO6P</t>
+  </si>
+  <si>
+    <t>exuwtvje@bientotmail.com</t>
+  </si>
+  <si>
+    <t>ajf256</t>
+  </si>
+  <si>
+    <t>E2SyMvDzebHiqL</t>
+  </si>
+  <si>
+    <t>MGM6VDUWYFMXTAVY</t>
+  </si>
+  <si>
+    <t>mazrqyry@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>lizik012</t>
+  </si>
+  <si>
+    <t>2TIwxbfGoNBSy6hJQ</t>
+  </si>
+  <si>
+    <t>AYRPIPJ6J7PCQAUB</t>
+  </si>
+  <si>
+    <t>vqgqgoid@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>moro1103</t>
+  </si>
+  <si>
+    <t>36IqbAkQ94OhS2oDU</t>
+  </si>
+  <si>
+    <t>2RZ7LNKJMOUU5MTY</t>
+  </si>
+  <si>
+    <t>bbnxthzq@bientotmail.com</t>
+  </si>
+  <si>
+    <t>firetribe79</t>
+  </si>
+  <si>
+    <t>byoIpudQA9NGsJSXCg</t>
+  </si>
+  <si>
+    <t>734ACUA3AKZX6RO3</t>
+  </si>
+  <si>
+    <t>nzxbzhnj@bonsoirmail.com</t>
+  </si>
+  <si>
+    <t>IyayiFred</t>
+  </si>
+  <si>
+    <t>Os9oqAdCXmHIcGwj</t>
+  </si>
+  <si>
+    <t>6Q66K44R2MRGWX3W</t>
+  </si>
+  <si>
+    <t>spoeveyh@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>hashtagPanthers</t>
+  </si>
+  <si>
+    <t>yJCtBWcz64eNFwxj</t>
+  </si>
+  <si>
+    <t>AYFWIGA6HE7CIN6C</t>
+  </si>
+  <si>
+    <t>dxrqnwfj@aurevoirmail.com</t>
+  </si>
+  <si>
+    <t>antoxa9210</t>
+  </si>
+  <si>
+    <t>ESiLVs1OW2pGC0Pvau</t>
+  </si>
+  <si>
+    <t>3OODIKW2RZ3U6OXR</t>
+  </si>
+  <si>
+    <t>sroycuot@bonjourfmail.com</t>
+  </si>
+  <si>
+    <t>mariajulianape3</t>
+  </si>
+  <si>
+    <t>dpgyrqnzBRome2tP</t>
+  </si>
+  <si>
+    <t>5UY2XBDMWBZJD4EH</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2555,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -2923,353 +3343,843 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="3" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="3" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="3" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" s="3" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D67" s="3" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="3" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="3" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="3" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" s="3" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D72" s="3" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D73" s="3" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="3" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="3" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="3" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="3" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="D78" s="3" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="3" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="5" t="s">
+      <c r="A80" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="3" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D81" s="3" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="3" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D83" s="3" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D84" s="3" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="D85" s="3" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="D86" s="3" t="s">
         <v>304</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
   <si>
     <t>email</t>
   </si>
@@ -522,6 +522,246 @@
   </si>
   <si>
     <t>OLQFNSND2SOPVIKW</t>
+  </si>
+  <si>
+    <t>vrrjvyri@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>blanenash</t>
+  </si>
+  <si>
+    <t>kFoGygECnQeq4mlt</t>
+  </si>
+  <si>
+    <t>OJSSCPC2OCBFTZ5L</t>
+  </si>
+  <si>
+    <t>mexdkilg@streetwormail.com</t>
+  </si>
+  <si>
+    <t>ChanDelhi</t>
+  </si>
+  <si>
+    <t>xekDK2M0caNhTp</t>
+  </si>
+  <si>
+    <t>OKG6U2Q7GJX7VN3C</t>
+  </si>
+  <si>
+    <t>nbvxdoyc@wildbmail.com</t>
+  </si>
+  <si>
+    <t>DebZambrana</t>
+  </si>
+  <si>
+    <t>HJp2XYE5zRaceOkjM</t>
+  </si>
+  <si>
+    <t>OQUZCWG4ZTWRNS3A</t>
+  </si>
+  <si>
+    <t>sliquyso@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>justifiedlus</t>
+  </si>
+  <si>
+    <t>RKI8UyOi9bapjJe</t>
+  </si>
+  <si>
+    <t>OLPHR3KQRCB76VF3</t>
+  </si>
+  <si>
+    <t>lcnosdnd@eblanomail.com</t>
+  </si>
+  <si>
+    <t>Chelsea912</t>
+  </si>
+  <si>
+    <t>bN9hUzV1MOyPui8fxT</t>
+  </si>
+  <si>
+    <t>ODDXHWLABAJ57TQU</t>
+  </si>
+  <si>
+    <t>objgraen@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>DCheavacci</t>
+  </si>
+  <si>
+    <t>CqRBSsKDY5O63E</t>
+  </si>
+  <si>
+    <t>OEOTT2GFNBO7PDWE</t>
+  </si>
+  <si>
+    <t>kcksbndp@tubermail.com</t>
+  </si>
+  <si>
+    <t>haylie_hebner</t>
+  </si>
+  <si>
+    <t>XUEicPQ3kMDRauN</t>
+  </si>
+  <si>
+    <t>OLFBWLLNNP7NRW2S</t>
+  </si>
+  <si>
+    <t>kmdddlkc@tubermail.com</t>
+  </si>
+  <si>
+    <t>Bmwljw1946Linda</t>
+  </si>
+  <si>
+    <t>BL2KSWoQbstZ4DHz</t>
+  </si>
+  <si>
+    <t>OT4F64JFZCNIX534</t>
+  </si>
+  <si>
+    <t>cfvcdgmk@tubermail.com</t>
+  </si>
+  <si>
+    <t>Bammypop</t>
+  </si>
+  <si>
+    <t>wEq54C7jT6KefZs</t>
+  </si>
+  <si>
+    <t>OFJX2POCKTIRR3TK</t>
+  </si>
+  <si>
+    <t>utnxcfcw@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>DanDolana</t>
+  </si>
+  <si>
+    <t>GhQZsfiNIH2d5D0oue</t>
+  </si>
+  <si>
+    <t>ONTAQWS6CDR2PS7L</t>
+  </si>
+  <si>
+    <t>hqbusrhd@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>iulya_daniela</t>
+  </si>
+  <si>
+    <t>qIPVQmB3KJ78d0</t>
+  </si>
+  <si>
+    <t>OSZ2K3XJ7B3E7MQ4</t>
+  </si>
+  <si>
+    <t>shzbhzqs@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>ffamm1</t>
+  </si>
+  <si>
+    <t>rvMpuhBSG0sqHJfPl</t>
+  </si>
+  <si>
+    <t>OU53J46HGJ5UI6FN</t>
+  </si>
+  <si>
+    <t>jozpospu@tubermail.com</t>
+  </si>
+  <si>
+    <t>eyesonthee</t>
+  </si>
+  <si>
+    <t>l3ZVuW92h184cJsEOM</t>
+  </si>
+  <si>
+    <t>OHCKFRP5YZ4N5OWF</t>
+  </si>
+  <si>
+    <t>cjrnnfhe@streetwormail.com</t>
+  </si>
+  <si>
+    <t>Azegah</t>
+  </si>
+  <si>
+    <t>shzJvkYRijDfqX</t>
+  </si>
+  <si>
+    <t>ORXRZGPBHUCPOB5X</t>
+  </si>
+  <si>
+    <t>nvmzbuov@eblanomail.com</t>
+  </si>
+  <si>
+    <t>CraigBurreson</t>
+  </si>
+  <si>
+    <t>EORPmUxZiu02jktI</t>
+  </si>
+  <si>
+    <t>OQMMCQJQ5MVFMXDF</t>
+  </si>
+  <si>
+    <t>ukkgrivr@wildbmail.com</t>
+  </si>
+  <si>
+    <t>Alesssadrovs</t>
+  </si>
+  <si>
+    <t>KU2t7VpyS9PAR3FB</t>
+  </si>
+  <si>
+    <t>OQSWOOYUCHBZ6F5L</t>
+  </si>
+  <si>
+    <t>vzxuucmf@streetwormail.com</t>
+  </si>
+  <si>
+    <t>debichessmabie</t>
+  </si>
+  <si>
+    <t>xRfUGZmCXKtP31iynD</t>
+  </si>
+  <si>
+    <t>OII6J2E7MUGTXQPO</t>
+  </si>
+  <si>
+    <t>holendri@tubermail.com</t>
+  </si>
+  <si>
+    <t>DavidWilt16</t>
+  </si>
+  <si>
+    <t>2acqFrnHef34mogh</t>
+  </si>
+  <si>
+    <t>OOCG4VHNNU6AGSR3</t>
+  </si>
+  <si>
+    <t>enszclqy@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>kim_goldie</t>
+  </si>
+  <si>
+    <t>9OdGCsPmYolKHNtUv</t>
+  </si>
+  <si>
+    <t>OT3WY2EVGPWXGBTF</t>
+  </si>
+  <si>
+    <t>ynrjpyck@eblanomail.com</t>
+  </si>
+  <si>
+    <t>Clara01234562</t>
+  </si>
+  <si>
+    <t>rdRIUJLy4bZxh0</t>
+  </si>
+  <si>
+    <t>OUH2JWRUWGKGCPM5</t>
   </si>
 </sst>
 </file>
@@ -534,14 +774,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1041,151 +1274,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1711,7 +1943,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -1739,142 +1971,142 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:4">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2296,6 +2528,286 @@
       </c>
       <c r="D41" s="2" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>169</v>
+      </c>
+      <c r="B43" t="s">
+        <v>170</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D43" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" t="s">
+        <v>186</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D47" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D48" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>193</v>
+      </c>
+      <c r="B49" t="s">
+        <v>194</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" t="s">
+        <v>202</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D51" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" t="s">
+        <v>206</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D52" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>213</v>
+      </c>
+      <c r="B54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D54" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>217</v>
+      </c>
+      <c r="B55" t="s">
+        <v>218</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D55" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>221</v>
+      </c>
+      <c r="B56" t="s">
+        <v>222</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D56" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>225</v>
+      </c>
+      <c r="B57" t="s">
+        <v>226</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D57" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>229</v>
+      </c>
+      <c r="B58" t="s">
+        <v>230</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D58" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>233</v>
+      </c>
+      <c r="B59" t="s">
+        <v>234</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D59" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>237</v>
+      </c>
+      <c r="B60" t="s">
+        <v>238</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>241</v>
+      </c>
+      <c r="B61" t="s">
+        <v>242</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D61" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27810" windowHeight="13470"/>
+    <workbookView windowWidth="19875" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
   <si>
     <t>email</t>
   </si>
@@ -762,6 +762,246 @@
   </si>
   <si>
     <t>OUH2JWRUWGKGCPM5</t>
+  </si>
+  <si>
+    <t>svqttxyh@streetwormail.com</t>
+  </si>
+  <si>
+    <t>AutosThen</t>
+  </si>
+  <si>
+    <t>JRNfCXmod1lSxF8E5b</t>
+  </si>
+  <si>
+    <t>PNNIZOYQNMHPNJ37</t>
+  </si>
+  <si>
+    <t>fcmpsfch@eblanomail.com</t>
+  </si>
+  <si>
+    <t>alpumpman29</t>
+  </si>
+  <si>
+    <t>A6ibhMgZJLqdyc9j4H</t>
+  </si>
+  <si>
+    <t>PG4VRIIQLRIAOJYB</t>
+  </si>
+  <si>
+    <t>rwztpzli@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>OhhDaaanny</t>
+  </si>
+  <si>
+    <t>dHqQOyEkXZtmgn9</t>
+  </si>
+  <si>
+    <t>PNAL3T2SUEDLZQQA</t>
+  </si>
+  <si>
+    <t>yqydnqeo@streetwormail.com</t>
+  </si>
+  <si>
+    <t>AnitaKukua</t>
+  </si>
+  <si>
+    <t>5wSZ8DK1Ij0OWaX</t>
+  </si>
+  <si>
+    <t>PMC24ZA6GKDSLTGD</t>
+  </si>
+  <si>
+    <t>rlkskggm@wildbmail.com</t>
+  </si>
+  <si>
+    <t>CrihsRibeiro</t>
+  </si>
+  <si>
+    <t>Sh0C5F2a6GBbJkgo1M</t>
+  </si>
+  <si>
+    <t>PNU3ZUTR5IDNDK65</t>
+  </si>
+  <si>
+    <t>kmkotpxl@eblanomail.com</t>
+  </si>
+  <si>
+    <t>Darkwish77</t>
+  </si>
+  <si>
+    <t>fURpqVuaQ07FW94AP</t>
+  </si>
+  <si>
+    <t>POCJKE6O7SIHEYW7</t>
+  </si>
+  <si>
+    <t>dgkwlzsl@eblanomail.com</t>
+  </si>
+  <si>
+    <t>tstevens1387</t>
+  </si>
+  <si>
+    <t>jF6S42EQNWaDwJKz</t>
+  </si>
+  <si>
+    <t>PC3SVABL65EIVXJR</t>
+  </si>
+  <si>
+    <t>kudonqso@tubermail.com</t>
+  </si>
+  <si>
+    <t>yourbrownsugart</t>
+  </si>
+  <si>
+    <t>SQKgNadoJM0Yqtf3</t>
+  </si>
+  <si>
+    <t>PINS5PRPN2GLT6HG</t>
+  </si>
+  <si>
+    <t>xxmwsykm@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>ptitekroline</t>
+  </si>
+  <si>
+    <t>jSbOvu8rTot1p0</t>
+  </si>
+  <si>
+    <t>POWJMQ2LHBDCHPE2</t>
+  </si>
+  <si>
+    <t>fkpjekyp@streetwormail.com</t>
+  </si>
+  <si>
+    <t>AntonioUngaro78</t>
+  </si>
+  <si>
+    <t>7d9nFlOXHgvYri</t>
+  </si>
+  <si>
+    <t>PCFG2EWMJYCGJJWR</t>
+  </si>
+  <si>
+    <t>jzwhanpu@tubermail.com</t>
+  </si>
+  <si>
+    <t>Andrewryan0321</t>
+  </si>
+  <si>
+    <t>5KR0DOMUYlozcCd</t>
+  </si>
+  <si>
+    <t>P7BHRSMPZUXZ3BBT</t>
+  </si>
+  <si>
+    <t>swhxzcey@streetwormail.com</t>
+  </si>
+  <si>
+    <t>AmesJesse</t>
+  </si>
+  <si>
+    <t>fCzAnu2xlgN467FYV</t>
+  </si>
+  <si>
+    <t>PNYBB2LBNG7NNN6E</t>
+  </si>
+  <si>
+    <t>uvgaowai@streetwormail.com</t>
+  </si>
+  <si>
+    <t>Daniela_Diaz_f</t>
+  </si>
+  <si>
+    <t>g0E3Xeilz4b18yA</t>
+  </si>
+  <si>
+    <t>PCMHHZ46D3KMCJWA</t>
+  </si>
+  <si>
+    <t>rbhhwnrv@eblanomail.com</t>
+  </si>
+  <si>
+    <t>Carlos95057748</t>
+  </si>
+  <si>
+    <t>7Is5Zgb9Siny816wPR</t>
+  </si>
+  <si>
+    <t>PL6X4CYEHCZ6IPCM</t>
+  </si>
+  <si>
+    <t>zbmautca@wildbmail.com</t>
+  </si>
+  <si>
+    <t>BlackAngel891</t>
+  </si>
+  <si>
+    <t>D6wOMjibzT2HPpJ</t>
+  </si>
+  <si>
+    <t>PPV43OBCRWSSRIY7</t>
+  </si>
+  <si>
+    <t>fnjqjxol@eblanomail.com</t>
+  </si>
+  <si>
+    <t>Blandine10200</t>
+  </si>
+  <si>
+    <t>eqpoHskgTAivWC</t>
+  </si>
+  <si>
+    <t>PPH64TDSSC3LGRRE</t>
+  </si>
+  <si>
+    <t>ueddwihe@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>Dany_Emad</t>
+  </si>
+  <si>
+    <t>jI9GfeQhBADP5Oic7w</t>
+  </si>
+  <si>
+    <t>PHEUMHHYTJFDJLHU</t>
+  </si>
+  <si>
+    <t>dyhujqiz@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>jackielevy18</t>
+  </si>
+  <si>
+    <t>8UL4Az0MYchkErg6D</t>
+  </si>
+  <si>
+    <t>PDTGXOFQFDZP2TET</t>
+  </si>
+  <si>
+    <t>tiwviopn@eblanomail.com</t>
+  </si>
+  <si>
+    <t>DamyNoemi</t>
+  </si>
+  <si>
+    <t>jADS9iCOyKb1T0Vh3</t>
+  </si>
+  <si>
+    <t>PHAE55KMTG2DNC4Q</t>
+  </si>
+  <si>
+    <t>jsigrbor@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>CoolHind</t>
+  </si>
+  <si>
+    <t>SXHPcWLFNQxIoU3eA</t>
+  </si>
+  <si>
+    <t>PQNJZ3X6KCCESBPY</t>
   </si>
 </sst>
 </file>
@@ -1943,7 +2183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -2810,6 +3050,286 @@
         <v>244</v>
       </c>
     </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>245</v>
+      </c>
+      <c r="B62" t="s">
+        <v>246</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D62" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>249</v>
+      </c>
+      <c r="B63" t="s">
+        <v>250</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D63" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>253</v>
+      </c>
+      <c r="B64" t="s">
+        <v>254</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D64" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>257</v>
+      </c>
+      <c r="B65" t="s">
+        <v>258</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D65" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>261</v>
+      </c>
+      <c r="B66" t="s">
+        <v>262</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D66" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>265</v>
+      </c>
+      <c r="B67" t="s">
+        <v>266</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D67" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>269</v>
+      </c>
+      <c r="B68" t="s">
+        <v>270</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D68" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>273</v>
+      </c>
+      <c r="B69" t="s">
+        <v>274</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D69" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>277</v>
+      </c>
+      <c r="B70" t="s">
+        <v>278</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D70" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>281</v>
+      </c>
+      <c r="B71" t="s">
+        <v>282</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D71" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>285</v>
+      </c>
+      <c r="B72" t="s">
+        <v>286</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D72" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>289</v>
+      </c>
+      <c r="B73" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D73" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>293</v>
+      </c>
+      <c r="B74" t="s">
+        <v>294</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D74" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>297</v>
+      </c>
+      <c r="B75" t="s">
+        <v>298</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D75" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" t="s">
+        <v>302</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D76" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>305</v>
+      </c>
+      <c r="B77" t="s">
+        <v>306</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D77" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>309</v>
+      </c>
+      <c r="B78" t="s">
+        <v>310</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D78" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>313</v>
+      </c>
+      <c r="B79" t="s">
+        <v>314</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D79" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>317</v>
+      </c>
+      <c r="B80" t="s">
+        <v>318</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D80" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>321</v>
+      </c>
+      <c r="B81" t="s">
+        <v>322</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D81" t="s">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/twitter_account.xlsx
+++ b/twitter_account.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19875" windowHeight="17655"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="525">
   <si>
     <t>email</t>
   </si>
@@ -1002,6 +1002,606 @@
   </si>
   <si>
     <t>PQNJZ3X6KCCESBPY</t>
+  </si>
+  <si>
+    <t>ohmskged@wildbmail.com</t>
+  </si>
+  <si>
+    <t>xtrimchaos</t>
+  </si>
+  <si>
+    <t>9gWKFjDRiY</t>
+  </si>
+  <si>
+    <t>TOZMVUQAJPO4K6K3</t>
+  </si>
+  <si>
+    <t>udlotqts@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>RijalMuhaimin11</t>
+  </si>
+  <si>
+    <t>SALJaGg4mf</t>
+  </si>
+  <si>
+    <t>56JINH7HDG3JP26F</t>
+  </si>
+  <si>
+    <t>etcipbyc@eblanomail.com</t>
+  </si>
+  <si>
+    <t>sto_rcds</t>
+  </si>
+  <si>
+    <t>hEHh8xkUyZ</t>
+  </si>
+  <si>
+    <t>YGJF5P3D53UGEKHF</t>
+  </si>
+  <si>
+    <t>ikedymsp@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>kioswy</t>
+  </si>
+  <si>
+    <t>BejfXaBwwM</t>
+  </si>
+  <si>
+    <t>YM3NB6DIJX7ZNALP</t>
+  </si>
+  <si>
+    <t>kclfntym@tubermail.com</t>
+  </si>
+  <si>
+    <t>sdl6259</t>
+  </si>
+  <si>
+    <t>MMBpL6nrWd</t>
+  </si>
+  <si>
+    <t>LQ2ZXNJBJTGXYAPT</t>
+  </si>
+  <si>
+    <t>twuwstmx@streetwormail.com</t>
+  </si>
+  <si>
+    <t>mzainalmuttakin</t>
+  </si>
+  <si>
+    <t>BgDHZpEXf4</t>
+  </si>
+  <si>
+    <t>ZGH34N2BPPQAJBDP</t>
+  </si>
+  <si>
+    <t>tlihplow@eblanomail.com</t>
+  </si>
+  <si>
+    <t>Peedroootz</t>
+  </si>
+  <si>
+    <t>LxZ3HhZD2M</t>
+  </si>
+  <si>
+    <t>6KJJHUROCI45K56M</t>
+  </si>
+  <si>
+    <t>iojbkxma@eblanomail.com</t>
+  </si>
+  <si>
+    <t>gaston1441</t>
+  </si>
+  <si>
+    <t>7UjkukLW4D</t>
+  </si>
+  <si>
+    <t>IWUZ62P4PIKCGGJA</t>
+  </si>
+  <si>
+    <t>ponwncqc@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>Zicko0o0</t>
+  </si>
+  <si>
+    <t>tmD8x4SL8M</t>
+  </si>
+  <si>
+    <t>DAWXYMK72IX3ZQ2Q</t>
+  </si>
+  <si>
+    <t>bkorfqcm@wildbmail.com</t>
+  </si>
+  <si>
+    <t>FabianFabisfd</t>
+  </si>
+  <si>
+    <t>eKSRLgRgjq</t>
+  </si>
+  <si>
+    <t>3HMUC2ILGM63ZHFB</t>
+  </si>
+  <si>
+    <t>tskahyef@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>Juanma_453</t>
+  </si>
+  <si>
+    <t>NqzvytafCN</t>
+  </si>
+  <si>
+    <t>L2JZK2QSLRFHJKXJ</t>
+  </si>
+  <si>
+    <t>gjtruyhw@streetwormail.com</t>
+  </si>
+  <si>
+    <t>Milafoxf</t>
+  </si>
+  <si>
+    <t>qQSHjSsEup</t>
+  </si>
+  <si>
+    <t>RAKB7JD4QPOLIHDG</t>
+  </si>
+  <si>
+    <t>catnmhts@eblanomail.com</t>
+  </si>
+  <si>
+    <t>BallaCleusio</t>
+  </si>
+  <si>
+    <t>PgYswvX7KP</t>
+  </si>
+  <si>
+    <t>IYCHIJAVSI32KJ77</t>
+  </si>
+  <si>
+    <t>dsltzgko@streetwormail.com</t>
+  </si>
+  <si>
+    <t>chansuilung</t>
+  </si>
+  <si>
+    <t>tQzBDu5S5h</t>
+  </si>
+  <si>
+    <t>EN7G2QG7GFQJRTXV</t>
+  </si>
+  <si>
+    <t>uwnhgqju@tubermail.com</t>
+  </si>
+  <si>
+    <t>Eyad51987041</t>
+  </si>
+  <si>
+    <t>tkaVv9Kumw</t>
+  </si>
+  <si>
+    <t>ZHUH6AC4SOOTZ32R</t>
+  </si>
+  <si>
+    <t>cujepnqb@wildbmail.com</t>
+  </si>
+  <si>
+    <t>azael_89</t>
+  </si>
+  <si>
+    <t>UNSaSeDYKK</t>
+  </si>
+  <si>
+    <t>73P6UCUBOEGA3B2L</t>
+  </si>
+  <si>
+    <t>tlxvoqfi@streetwormail.com</t>
+  </si>
+  <si>
+    <t>PABLOCHAMORRO52</t>
+  </si>
+  <si>
+    <t>KNKhwkPm7P</t>
+  </si>
+  <si>
+    <t>AVUMQWB3FPIYYMUQ</t>
+  </si>
+  <si>
+    <t>nzfxhqrv@wildbmail.com</t>
+  </si>
+  <si>
+    <t>michael09744071</t>
+  </si>
+  <si>
+    <t>F2GEVzBHym</t>
+  </si>
+  <si>
+    <t>TBBPFCODLFM5Y6A5</t>
+  </si>
+  <si>
+    <t>gvdtnevx@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>Kstartng89</t>
+  </si>
+  <si>
+    <t>yF6zyP4FPY</t>
+  </si>
+  <si>
+    <t>6NKQURPDGEQMVXWM</t>
+  </si>
+  <si>
+    <t>aptwccud@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>FCamppTTV</t>
+  </si>
+  <si>
+    <t>qz8W4GQuSa</t>
+  </si>
+  <si>
+    <t>2UBZPJU35EHFXWCH</t>
+  </si>
+  <si>
+    <t>khxmkkcs@wildbmail.com</t>
+  </si>
+  <si>
+    <t>predatorslya</t>
+  </si>
+  <si>
+    <t>fqiPEi7jW3</t>
+  </si>
+  <si>
+    <t>S64UDXQXI2PJQ6LP</t>
+  </si>
+  <si>
+    <t>kavwhrsn@streetwormail.com</t>
+  </si>
+  <si>
+    <t>conloli01</t>
+  </si>
+  <si>
+    <t>7H5BuucMyu</t>
+  </si>
+  <si>
+    <t>XYPVCQGZJYGXFET5</t>
+  </si>
+  <si>
+    <t>wnhvltis@eblanomail.com</t>
+  </si>
+  <si>
+    <t>Dckr_JD</t>
+  </si>
+  <si>
+    <t>GstjnRAmRe</t>
+  </si>
+  <si>
+    <t>P4T5GSAW3ML5SFWI</t>
+  </si>
+  <si>
+    <t>tvjlonag@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>rolinwalk</t>
+  </si>
+  <si>
+    <t>kN4U4DFTq3</t>
+  </si>
+  <si>
+    <t>FFRSSGZMQRBZJO37</t>
+  </si>
+  <si>
+    <t>zfpxoavy@wildbmail.com</t>
+  </si>
+  <si>
+    <t>AlaaMohamadin</t>
+  </si>
+  <si>
+    <t>ZSF3X6gqFQ</t>
+  </si>
+  <si>
+    <t>FTJ3IJMTMGEIUH3P</t>
+  </si>
+  <si>
+    <t>lwjbfzbo@wildbmail.com</t>
+  </si>
+  <si>
+    <t>adorable91226</t>
+  </si>
+  <si>
+    <t>5eZzJWQ3g3</t>
+  </si>
+  <si>
+    <t>PFLAYBRURF725HDL</t>
+  </si>
+  <si>
+    <t>bvpjdlnu@streetwormail.com</t>
+  </si>
+  <si>
+    <t>clerici_javier</t>
+  </si>
+  <si>
+    <t>xZfWUyafyV</t>
+  </si>
+  <si>
+    <t>LZ5GTWE7Y5GDAIYA</t>
+  </si>
+  <si>
+    <t>fghlymta@tubermail.com</t>
+  </si>
+  <si>
+    <t>Daniel46270802</t>
+  </si>
+  <si>
+    <t>aiVJeudyeS</t>
+  </si>
+  <si>
+    <t>DXRISPPZJJ62NUBO</t>
+  </si>
+  <si>
+    <t>vcpvmfcg@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>KamrulH84400594</t>
+  </si>
+  <si>
+    <t>t7D7UwFMxu</t>
+  </si>
+  <si>
+    <t>UFHXWTUJ6X2WLFAM</t>
+  </si>
+  <si>
+    <t>aomqugpq@eblanomail.com</t>
+  </si>
+  <si>
+    <t>OLallan283</t>
+  </si>
+  <si>
+    <t>v2WGLcCpE8</t>
+  </si>
+  <si>
+    <t>L5YTVIPPBJ6LAG2G</t>
+  </si>
+  <si>
+    <t>uadfdpae@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>madson_cameli</t>
+  </si>
+  <si>
+    <t>MbD3M6Yc2Z</t>
+  </si>
+  <si>
+    <t>JVY6I2XFV4GCWLGS</t>
+  </si>
+  <si>
+    <t>jkftswze@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>goffers10</t>
+  </si>
+  <si>
+    <t>6c7EwSYUaS</t>
+  </si>
+  <si>
+    <t>5DAG7GLTY4GNW4UR</t>
+  </si>
+  <si>
+    <t>dixuqskx@wildbmail.com</t>
+  </si>
+  <si>
+    <t>Felipef57938539</t>
+  </si>
+  <si>
+    <t>pFxsfYdGut</t>
+  </si>
+  <si>
+    <t>SNYRODE4AXKABOGN</t>
+  </si>
+  <si>
+    <t>jnatpuws@tubermail.com</t>
+  </si>
+  <si>
+    <t>GaviriaMia</t>
+  </si>
+  <si>
+    <t>bUZTxTNp9A</t>
+  </si>
+  <si>
+    <t>4Y3D7DGPOKFMWMTT</t>
+  </si>
+  <si>
+    <t>jbnoalhc@streetwormail.com</t>
+  </si>
+  <si>
+    <t>ToFu84845875</t>
+  </si>
+  <si>
+    <t>pjHCteLM5d</t>
+  </si>
+  <si>
+    <t>6KWTFUDQJBFMCZDN</t>
+  </si>
+  <si>
+    <t>cebhfrco@wildbmail.com</t>
+  </si>
+  <si>
+    <t>BlazingOG1</t>
+  </si>
+  <si>
+    <t>ZZ7a6W7NWx</t>
+  </si>
+  <si>
+    <t>Z6D36D4YK6D5OYUJ</t>
+  </si>
+  <si>
+    <t>oohxmluz@tubermail.com</t>
+  </si>
+  <si>
+    <t>atilla_master</t>
+  </si>
+  <si>
+    <t>E2hTjiHmwM</t>
+  </si>
+  <si>
+    <t>6FMJJYB2MONXLY5M</t>
+  </si>
+  <si>
+    <t>lhdjlnhv@tubermail.com</t>
+  </si>
+  <si>
+    <t>AlexanderArrob2</t>
+  </si>
+  <si>
+    <t>yBdeTMmDHk</t>
+  </si>
+  <si>
+    <t>FR3UHMX4HQ4KU3HE</t>
+  </si>
+  <si>
+    <t>ptswxqpa@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>holiztixf</t>
+  </si>
+  <si>
+    <t>VDiixSpMwd</t>
+  </si>
+  <si>
+    <t>U2G3K2U62HCKTAZU</t>
+  </si>
+  <si>
+    <t>eshwtych@wildbmail.com</t>
+  </si>
+  <si>
+    <t>danielgonzale12</t>
+  </si>
+  <si>
+    <t>gN3qGzvdG3</t>
+  </si>
+  <si>
+    <t>L7EQHCFTEAABNDFL</t>
+  </si>
+  <si>
+    <t>cqsjegar@eblanomail.com</t>
+  </si>
+  <si>
+    <t>josealbert101</t>
+  </si>
+  <si>
+    <t>HCjJASPcLA</t>
+  </si>
+  <si>
+    <t>WOQSNNNYIHMKMCOP</t>
+  </si>
+  <si>
+    <t>cffwqqdb@ronaldofmail.com</t>
+  </si>
+  <si>
+    <t>ColmMHeaney</t>
+  </si>
+  <si>
+    <t>QgCMmV7RFd</t>
+  </si>
+  <si>
+    <t>IJYPLWWHDOCGEBLH</t>
+  </si>
+  <si>
+    <t>vkzgfoek@streetwormail.com</t>
+  </si>
+  <si>
+    <t>PhotoniaProFilm</t>
+  </si>
+  <si>
+    <t>HfM9yvre2h</t>
+  </si>
+  <si>
+    <t>IPMX7GGEBG6OCMZB</t>
+  </si>
+  <si>
+    <t>geixillw@streetwormail.com</t>
+  </si>
+  <si>
+    <t>LIDIACERDA1</t>
+  </si>
+  <si>
+    <t>iXzFe9CMas</t>
+  </si>
+  <si>
+    <t>YOUEASZGEF5T2VBK</t>
+  </si>
+  <si>
+    <t>sgumkyon@streetwormail.com</t>
+  </si>
+  <si>
+    <t>PajaricosWeb</t>
+  </si>
+  <si>
+    <t>tNtHvAR8Pa</t>
+  </si>
+  <si>
+    <t>G26JISTPONFFT7EK</t>
+  </si>
+  <si>
+    <t>zgewkmvf@wildbmail.com</t>
+  </si>
+  <si>
+    <t>CriminalValues</t>
+  </si>
+  <si>
+    <t>2SaJHvHTYj</t>
+  </si>
+  <si>
+    <t>R5K4L46FGDCVN5ZX</t>
+  </si>
+  <si>
+    <t>tzqdiodw@tubermail.com</t>
+  </si>
+  <si>
+    <t>YmaqEst</t>
+  </si>
+  <si>
+    <t>eF9YCkLW7n</t>
+  </si>
+  <si>
+    <t>A2VGCJQUK3JPKADX</t>
+  </si>
+  <si>
+    <t>wgopjrzs@wildbmail.com</t>
+  </si>
+  <si>
+    <t>achekoudm</t>
+  </si>
+  <si>
+    <t>qPUT8DftgH</t>
+  </si>
+  <si>
+    <t>KJNWDGKTGRG6Z2GE</t>
+  </si>
+  <si>
+    <t>omajftoh@eblanomail.com</t>
+  </si>
+  <si>
+    <t>DavidCr29705984</t>
+  </si>
+  <si>
+    <t>TkdJQY8hHB</t>
+  </si>
+  <si>
+    <t>PNXTZP5DHZJKSVLQ</t>
+  </si>
+  <si>
+    <t>tmqtetig@eblanomail.com</t>
+  </si>
+  <si>
+    <t>virus31erik</t>
+  </si>
+  <si>
+    <t>VJGsymMVvN</t>
+  </si>
+  <si>
+    <t>PLQLFSB4B32BODMG</t>
   </si>
 </sst>
 </file>
@@ -2183,7 +2783,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="36.0583333333333" customWidth="1"/>
@@ -3330,6 +3930,706 @@
         <v>324</v>
       </c>
     </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>325</v>
+      </c>
+      <c r="B82" t="s">
+        <v>326</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D82" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>329</v>
+      </c>
+      <c r="B83" t="s">
+        <v>330</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D83" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>333</v>
+      </c>
+      <c r="B84" t="s">
+        <v>334</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D84" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>337</v>
+      </c>
+      <c r="B85" t="s">
+        <v>338</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D85" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>341</v>
+      </c>
+      <c r="B86" t="s">
+        <v>342</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D86" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>345</v>
+      </c>
+      <c r="B87" t="s">
+        <v>346</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D87" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>349</v>
+      </c>
+      <c r="B88" t="s">
+        <v>350</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D88" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>353</v>
+      </c>
+      <c r="B89" t="s">
+        <v>354</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D89" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>357</v>
+      </c>
+      <c r="B90" t="s">
+        <v>358</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D90" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>361</v>
+      </c>
+      <c r="B91" t="s">
+        <v>362</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D91" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>365</v>
+      </c>
+      <c r="B92" t="s">
+        <v>366</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D92" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>369</v>
+      </c>
+      <c r="B93" t="s">
+        <v>370</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D93" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>373</v>
+      </c>
+      <c r="B94" t="s">
+        <v>374</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D94" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>377</v>
+      </c>
+      <c r="B95" t="s">
+        <v>378</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D95" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>381</v>
+      </c>
+      <c r="B96" t="s">
+        <v>382</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D96" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>385</v>
+      </c>
+      <c r="B97" t="s">
+        <v>386</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D97" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>389</v>
+      </c>
+      <c r="B98" t="s">
+        <v>390</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D98" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>393</v>
+      </c>
+      <c r="B99" t="s">
+        <v>394</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D99" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>397</v>
+      </c>
+      <c r="B100" t="s">
+        <v>398</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D100" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>401</v>
+      </c>
+      <c r="B101" t="s">
+        <v>402</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D101" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>405</v>
+      </c>
+      <c r="B102" t="s">
+        <v>406</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D102" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>409</v>
+      </c>
+      <c r="B103" t="s">
+        <v>410</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D103" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>413</v>
+      </c>
+      <c r="B104" t="s">
+        <v>414</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D104" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>417</v>
+      </c>
+      <c r="B105" t="s">
+        <v>418</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D105" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>421</v>
+      </c>
+      <c r="B106" t="s">
+        <v>422</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D106" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>425</v>
+      </c>
+      <c r="B107" t="s">
+        <v>426</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D107" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>429</v>
+      </c>
+      <c r="B108" t="s">
+        <v>430</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D108" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>433</v>
+      </c>
+      <c r="B109" t="s">
+        <v>434</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D109" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>437</v>
+      </c>
+      <c r="B110" t="s">
+        <v>438</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D110" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>441</v>
+      </c>
+      <c r="B111" t="s">
+        <v>442</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D111" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>445</v>
+      </c>
+      <c r="B112" t="s">
+        <v>446</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D112" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>449</v>
+      </c>
+      <c r="B113" t="s">
+        <v>450</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D113" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>453</v>
+      </c>
+      <c r="B114" t="s">
+        <v>454</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D114" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>457</v>
+      </c>
+      <c r="B115" t="s">
+        <v>458</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D115" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>461</v>
+      </c>
+      <c r="B116" t="s">
+        <v>462</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D116" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>465</v>
+      </c>
+      <c r="B117" t="s">
+        <v>466</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D117" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>469</v>
+      </c>
+      <c r="B118" t="s">
+        <v>470</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D118" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>473</v>
+      </c>
+      <c r="B119" t="s">
+        <v>474</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D119" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>477</v>
+      </c>
+      <c r="B120" t="s">
+        <v>478</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D120" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>481</v>
+      </c>
+      <c r="B121" t="s">
+        <v>482</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D121" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>485</v>
+      </c>
+      <c r="B122" t="s">
+        <v>486</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D122" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>489</v>
+      </c>
+      <c r="B123" t="s">
+        <v>490</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D123" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>493</v>
+      </c>
+      <c r="B124" t="s">
+        <v>494</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D124" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>497</v>
+      </c>
+      <c r="B125" t="s">
+        <v>498</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D125" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>501</v>
+      </c>
+      <c r="B126" t="s">
+        <v>502</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D126" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>505</v>
+      </c>
+      <c r="B127" t="s">
+        <v>506</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D127" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>509</v>
+      </c>
+      <c r="B128" t="s">
+        <v>510</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D128" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>513</v>
+      </c>
+      <c r="B129" t="s">
+        <v>514</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D129" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>517</v>
+      </c>
+      <c r="B130" t="s">
+        <v>518</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D130" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>521</v>
+      </c>
+      <c r="B131" t="s">
+        <v>522</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D131" t="s">
+        <v>524</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
